--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_grids\SuppXLS\trades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5474F874-8FA6-48A8-BDA6-F0269EA67C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F1927A-75E4-44DC-8502-B76422CFCD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="398">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -1225,6 +1224,12 @@
   </si>
   <si>
     <t>U</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>ELCNGA</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7AD9006-1C2C-46F0-B0FB-BDF459C7A9A0}">
-  <dimension ref="B3:Y160"/>
+  <dimension ref="B3:AG160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="19" max="19" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -1615,7 +1620,7 @@
     <col min="25" max="25" width="7.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1625,8 +1630,11 @@
       <c r="S3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="AA3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -1675,8 +1683,29 @@
       <c r="Y4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="AA4" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1728,8 +1757,30 @@
       <c r="Y5" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="AA5" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>396</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>397</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>396</v>
+      </c>
+      <c r="AF5" t="str">
+        <f>"TU_"&amp;AD5</f>
+        <v>TU_ELCNGA</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1782,7 +1833,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1835,7 +1886,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1888,7 +1939,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -1941,7 +1992,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1994,7 +2045,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -2047,7 +2098,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -2100,7 +2151,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -2153,7 +2204,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -2206,7 +2257,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -2259,7 +2310,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:33" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>8</v>
       </c>

--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F1927A-75E4-44DC-8502-B76422CFCD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0333645F-A614-4A0C-97DE-D17C8C33795A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
+    <sheet name="Uni" sheetId="2" r:id="rId2"/>
+    <sheet name="Bi" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="410">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -1230,13 +1232,49 @@
   </si>
   <si>
     <t>ELCNGA</t>
+  </si>
+  <si>
+    <t>~TradeLinks</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>PET</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>FOL</t>
+  </si>
+  <si>
+    <t>JET</t>
+  </si>
+  <si>
+    <t>OTH</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>NGA</t>
+  </si>
+  <si>
+    <t>DID</t>
+  </si>
+  <si>
+    <t>DIJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1251,16 +1289,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1268,16 +1350,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFC000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFC000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{2E24F3C1-4C57-4DFE-97FC-E41181489BC3}"/>
     <cellStyle name="Percent 2" xfId="1" xr:uid="{0BE1950C-59CF-4745-B2E6-140F8E2B482A}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -9230,4 +9347,426 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83540081-FFBC-45CD-9805-E20E8DB7BB2A}">
+  <dimension ref="C7:E62"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="9.19921875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C8" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C9" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C10" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C11" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C13" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C14" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C15" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C16" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C18" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C19" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C20" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C21" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C23" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C24" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C25" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C26" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="6"/>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C28" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C29" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C30" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C31" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C33" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C34" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C35" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C36" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C38" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C39" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C40" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C41" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C43" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C44" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C45" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C46" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C50" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C51" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C52" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C54" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C55" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C56" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C57" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D57" s="7"/>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C59" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C60" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C61" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="E61" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="C62" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D31F490-2E60-4CD9-970B-C57E29805C10}">
+  <dimension ref="B4:D7"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="9.06640625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:4" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B4" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="2:4" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B6" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B7" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>
--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0333645F-A614-4A0C-97DE-D17C8C33795A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D6169-E3BB-4AD3-9271-B92862BCF238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="412">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -1268,6 +1268,12 @@
   </si>
   <si>
     <t>DIJ</t>
+  </si>
+  <si>
+    <t>g_inter-island_HVDC</t>
+  </si>
+  <si>
+    <t>Inter-island HVDC connection</t>
   </si>
 </sst>
 </file>
@@ -1727,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7AD9006-1C2C-46F0-B0FB-BDF459C7A9A0}">
-  <dimension ref="B3:AG160"/>
+  <dimension ref="B3:AK160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="19" max="19" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -1737,7 +1743,7 @@
     <col min="25" max="25" width="7.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -1751,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -1822,7 +1828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1897,7 +1903,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1950,7 +1956,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -2003,7 +2009,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -2108,8 +2114,14 @@
       <c r="Y9" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="AA9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -2161,8 +2173,35 @@
       <c r="Y10" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="AA10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>294</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -2214,8 +2253,36 @@
       <c r="Y11" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="12" spans="2:33" x14ac:dyDescent="0.45">
+      <c r="AA11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>410</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ11" t="str">
+        <f>AF11</f>
+        <v>g_inter-island_HVDC</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="12" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -2268,7 +2335,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -2321,7 +2388,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -2374,7 +2441,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -2427,7 +2494,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>8</v>
       </c>

--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D6169-E3BB-4AD3-9271-B92862BCF238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C138FA-E4EC-4359-ABA9-363C5B650D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
     <sheet name="Uni" sheetId="2" r:id="rId2"/>
-    <sheet name="Bi" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="412">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -1377,7 +1376,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1396,7 +1395,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9786,54 +9784,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D31F490-2E60-4CD9-970B-C57E29805C10}">
-  <dimension ref="B4:D7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="16384" width="9.06640625" style="8"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="2:4" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B4" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="2:4" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B7" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C138FA-E4EC-4359-ABA9-363C5B650D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04DD684-02DE-42D1-99D4-42F269C4C48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2017" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="416">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -1273,6 +1273,18 @@
   </si>
   <si>
     <t>Inter-island HVDC connection</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>bioenergy</t>
+  </si>
+  <si>
+    <t>WOD</t>
   </si>
 </sst>
 </file>
@@ -1739,6 +1751,7 @@
     <col min="21" max="23" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="16.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:37" x14ac:dyDescent="0.45">
@@ -1890,8 +1903,9 @@
       <c r="AD5" t="s">
         <v>397</v>
       </c>
-      <c r="AE5" t="s">
-        <v>396</v>
+      <c r="AE5" t="str">
+        <f>AC5</f>
+        <v>gas</v>
       </c>
       <c r="AF5" t="str">
         <f>"TU_"&amp;AD5</f>
@@ -1953,6 +1967,29 @@
       <c r="Y6" t="s">
         <v>395</v>
       </c>
+      <c r="AA6" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>412</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>405</v>
+      </c>
+      <c r="AE6" t="str">
+        <f>AC6</f>
+        <v>coal</v>
+      </c>
+      <c r="AF6" t="str">
+        <f>"TU_ELC"&amp;AD6</f>
+        <v>TU_ELCCOA</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
@@ -2006,6 +2043,29 @@
       <c r="Y7" t="s">
         <v>395</v>
       </c>
+      <c r="AA7" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>413</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>401</v>
+      </c>
+      <c r="AE7" t="str">
+        <f t="shared" ref="AE7:AE8" si="3">AC7</f>
+        <v>oil</v>
+      </c>
+      <c r="AF7" t="str">
+        <f t="shared" ref="AF7:AF8" si="4">"TU_ELC"&amp;AD7</f>
+        <v>TU_ELCDSL</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
@@ -2045,11 +2105,11 @@
         <v>192</v>
       </c>
       <c r="V8" t="str">
-        <f t="shared" ref="V8:W8" si="3">U8</f>
+        <f t="shared" ref="V8:W8" si="5">U8</f>
         <v>e_w61853727-220</v>
       </c>
       <c r="W8" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>e_w61853727-220</v>
       </c>
       <c r="X8" t="str">
@@ -2059,6 +2119,29 @@
       <c r="Y8" t="s">
         <v>395</v>
       </c>
+      <c r="AA8" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>414</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>415</v>
+      </c>
+      <c r="AE8" t="str">
+        <f t="shared" si="3"/>
+        <v>bioenergy</v>
+      </c>
+      <c r="AF8" t="str">
+        <f t="shared" si="4"/>
+        <v>TU_ELCWOD</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="9" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
@@ -2098,11 +2181,11 @@
         <v>221</v>
       </c>
       <c r="V9" t="str">
-        <f t="shared" ref="V9:W9" si="4">U9</f>
+        <f t="shared" ref="V9:W9" si="6">U9</f>
         <v>e_w75609279-220</v>
       </c>
       <c r="W9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>e_w75609279-220</v>
       </c>
       <c r="X9" t="str">
@@ -2112,12 +2195,6 @@
       <c r="Y9" t="s">
         <v>395</v>
       </c>
-      <c r="AA9" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>293</v>
-      </c>
     </row>
     <row r="10" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
@@ -2157,11 +2234,11 @@
         <v>150</v>
       </c>
       <c r="V10" t="str">
-        <f t="shared" ref="V10:W10" si="5">U10</f>
+        <f t="shared" ref="V10:W10" si="7">U10</f>
         <v>e_w82881422-220</v>
       </c>
       <c r="W10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>e_w82881422-220</v>
       </c>
       <c r="X10" t="str">
@@ -2171,33 +2248,6 @@
       <c r="Y10" t="s">
         <v>395</v>
       </c>
-      <c r="AA10" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>294</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>295</v>
-      </c>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
@@ -2237,11 +2287,11 @@
         <v>130</v>
       </c>
       <c r="V11" t="str">
-        <f t="shared" ref="V11:W11" si="6">U11</f>
+        <f t="shared" ref="V11:W11" si="8">U11</f>
         <v>e_w87837416-220</v>
       </c>
       <c r="W11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>e_w87837416-220</v>
       </c>
       <c r="X11" t="str">
@@ -2252,32 +2302,10 @@
         <v>395</v>
       </c>
       <c r="AA11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>410</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>13</v>
-      </c>
-      <c r="AJ11" t="str">
-        <f>AF11</f>
-        <v>g_inter-island_HVDC</v>
-      </c>
-      <c r="AK11" t="s">
-        <v>411</v>
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="2:37" x14ac:dyDescent="0.45">
@@ -2318,11 +2346,11 @@
         <v>11</v>
       </c>
       <c r="V12" t="str">
-        <f t="shared" ref="V12:W12" si="7">U12</f>
+        <f t="shared" ref="V12:W12" si="9">U12</f>
         <v>e_w87897292-220</v>
       </c>
       <c r="W12" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>e_w87897292-220</v>
       </c>
       <c r="X12" t="str">
@@ -2332,6 +2360,33 @@
       <c r="Y12" t="s">
         <v>395</v>
       </c>
+      <c r="AA12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>294</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="13" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
@@ -2371,11 +2426,11 @@
         <v>175</v>
       </c>
       <c r="V13" t="str">
-        <f t="shared" ref="V13:W13" si="8">U13</f>
+        <f t="shared" ref="V13:W13" si="10">U13</f>
         <v>e_w87928925-220</v>
       </c>
       <c r="W13" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>e_w87928925-220</v>
       </c>
       <c r="X13" t="str">
@@ -2385,6 +2440,34 @@
       <c r="Y13" t="s">
         <v>395</v>
       </c>
+      <c r="AA13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>410</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ13" t="str">
+        <f>AF13</f>
+        <v>g_inter-island_HVDC</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="14" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
@@ -2424,11 +2507,11 @@
         <v>33</v>
       </c>
       <c r="V14" t="str">
-        <f t="shared" ref="V14:W14" si="9">U14</f>
+        <f t="shared" ref="V14:W14" si="11">U14</f>
         <v>e_w89411122-220</v>
       </c>
       <c r="W14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>e_w89411122-220</v>
       </c>
       <c r="X14" t="str">
@@ -2477,11 +2560,11 @@
         <v>85</v>
       </c>
       <c r="V15" t="str">
-        <f t="shared" ref="V15:W15" si="10">U15</f>
+        <f t="shared" ref="V15:W15" si="12">U15</f>
         <v>e_w89635947-220</v>
       </c>
       <c r="W15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>e_w89635947-220</v>
       </c>
       <c r="X15" t="str">
@@ -2530,11 +2613,11 @@
         <v>83</v>
       </c>
       <c r="V16" t="str">
-        <f t="shared" ref="V16:W16" si="11">U16</f>
+        <f t="shared" ref="V16:W16" si="13">U16</f>
         <v>e_w89636266-220</v>
       </c>
       <c r="W16" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>e_w89636266-220</v>
       </c>
       <c r="X16" t="str">
@@ -2583,11 +2666,11 @@
         <v>260</v>
       </c>
       <c r="V17" t="str">
-        <f t="shared" ref="V17:W17" si="12">U17</f>
+        <f t="shared" ref="V17:W17" si="14">U17</f>
         <v>e_w89636510-220</v>
       </c>
       <c r="W17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>e_w89636510-220</v>
       </c>
       <c r="X17" t="str">
@@ -2636,11 +2719,11 @@
         <v>88</v>
       </c>
       <c r="V18" t="str">
-        <f t="shared" ref="V18:W18" si="13">U18</f>
+        <f t="shared" ref="V18:W18" si="15">U18</f>
         <v>e_w89637173-220</v>
       </c>
       <c r="W18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>e_w89637173-220</v>
       </c>
       <c r="X18" t="str">
@@ -2689,11 +2772,11 @@
         <v>264</v>
       </c>
       <c r="V19" t="str">
-        <f t="shared" ref="V19:W19" si="14">U19</f>
+        <f t="shared" ref="V19:W19" si="16">U19</f>
         <v>e_w89637174-220</v>
       </c>
       <c r="W19" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>e_w89637174-220</v>
       </c>
       <c r="X19" t="str">
@@ -2742,11 +2825,11 @@
         <v>201</v>
       </c>
       <c r="V20" t="str">
-        <f t="shared" ref="V20:W20" si="15">U20</f>
+        <f t="shared" ref="V20:W20" si="17">U20</f>
         <v>e_w89637277-220</v>
       </c>
       <c r="W20" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>e_w89637277-220</v>
       </c>
       <c r="X20" t="str">
@@ -2795,11 +2878,11 @@
         <v>104</v>
       </c>
       <c r="V21" t="str">
-        <f t="shared" ref="V21:W21" si="16">U21</f>
+        <f t="shared" ref="V21:W21" si="18">U21</f>
         <v>e_w270521928-220</v>
       </c>
       <c r="W21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>e_w270521928-220</v>
       </c>
       <c r="X21" t="str">
@@ -2848,11 +2931,11 @@
         <v>78</v>
       </c>
       <c r="V22" t="str">
-        <f t="shared" ref="V22:W22" si="17">U22</f>
+        <f t="shared" ref="V22:W22" si="19">U22</f>
         <v>e_w89664063-220</v>
       </c>
       <c r="W22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>e_w89664063-220</v>
       </c>
       <c r="X22" t="str">
@@ -2901,11 +2984,11 @@
         <v>270</v>
       </c>
       <c r="V23" t="str">
-        <f t="shared" ref="V23:W23" si="18">U23</f>
+        <f t="shared" ref="V23:W23" si="20">U23</f>
         <v>e_w89943957-220</v>
       </c>
       <c r="W23" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>e_w89943957-220</v>
       </c>
       <c r="X23" t="str">
@@ -2954,11 +3037,11 @@
         <v>272</v>
       </c>
       <c r="V24" t="str">
-        <f t="shared" ref="V24:W24" si="19">U24</f>
+        <f t="shared" ref="V24:W24" si="21">U24</f>
         <v>e_w90092620-220</v>
       </c>
       <c r="W24" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>e_w90092620-220</v>
       </c>
       <c r="X24" t="str">
@@ -3007,11 +3090,11 @@
         <v>188</v>
       </c>
       <c r="V25" t="str">
-        <f t="shared" ref="V25:W25" si="20">U25</f>
+        <f t="shared" ref="V25:W25" si="22">U25</f>
         <v>e_w90098853-220</v>
       </c>
       <c r="W25" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>e_w90098853-220</v>
       </c>
       <c r="X25" t="str">
@@ -3060,11 +3143,11 @@
         <v>227</v>
       </c>
       <c r="V26" t="str">
-        <f t="shared" ref="V26:W26" si="21">U26</f>
+        <f t="shared" ref="V26:W26" si="23">U26</f>
         <v>e_w93419960-220</v>
       </c>
       <c r="W26" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>e_w93419960-220</v>
       </c>
       <c r="X26" t="str">
@@ -3113,11 +3196,11 @@
         <v>251</v>
       </c>
       <c r="V27" t="str">
-        <f t="shared" ref="V27:W27" si="22">U27</f>
+        <f t="shared" ref="V27:W27" si="24">U27</f>
         <v>e_w93556808-220</v>
       </c>
       <c r="W27" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>e_w93556808-220</v>
       </c>
       <c r="X27" t="str">
@@ -3166,11 +3249,11 @@
         <v>168</v>
       </c>
       <c r="V28" t="str">
-        <f t="shared" ref="V28:W28" si="23">U28</f>
+        <f t="shared" ref="V28:W28" si="25">U28</f>
         <v>e_w93713118-220</v>
       </c>
       <c r="W28" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>e_w93713118-220</v>
       </c>
       <c r="X28" t="str">
@@ -3219,11 +3302,11 @@
         <v>215</v>
       </c>
       <c r="V29" t="str">
-        <f t="shared" ref="V29:W29" si="24">U29</f>
+        <f t="shared" ref="V29:W29" si="26">U29</f>
         <v>e_w93827784-220</v>
       </c>
       <c r="W29" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>e_w93827784-220</v>
       </c>
       <c r="X29" t="str">
@@ -3272,11 +3355,11 @@
         <v>281</v>
       </c>
       <c r="V30" t="str">
-        <f t="shared" ref="V30:W30" si="25">U30</f>
+        <f t="shared" ref="V30:W30" si="27">U30</f>
         <v>e_w94053861-220</v>
       </c>
       <c r="W30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>e_w94053861-220</v>
       </c>
       <c r="X30" t="str">
@@ -3325,11 +3408,11 @@
         <v>232</v>
       </c>
       <c r="V31" t="str">
-        <f t="shared" ref="V31:W31" si="26">U31</f>
+        <f t="shared" ref="V31:W31" si="28">U31</f>
         <v>e_w94840399-220</v>
       </c>
       <c r="W31" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>e_w94840399-220</v>
       </c>
       <c r="X31" t="str">
@@ -3378,11 +3461,11 @@
         <v>285</v>
       </c>
       <c r="V32" t="str">
-        <f t="shared" ref="V32:W32" si="27">U32</f>
+        <f t="shared" ref="V32:W32" si="29">U32</f>
         <v>e_w95046918-220</v>
       </c>
       <c r="W32" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>e_w95046918-220</v>
       </c>
       <c r="X32" t="str">
@@ -3431,11 +3514,11 @@
         <v>217</v>
       </c>
       <c r="V33" t="str">
-        <f t="shared" ref="V33:W33" si="28">U33</f>
+        <f t="shared" ref="V33:W33" si="30">U33</f>
         <v>e_w95048289-220</v>
       </c>
       <c r="W33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>e_w95048289-220</v>
       </c>
       <c r="X33" t="str">
@@ -3484,11 +3567,11 @@
         <v>279</v>
       </c>
       <c r="V34" t="str">
-        <f t="shared" ref="V34:W34" si="29">U34</f>
+        <f t="shared" ref="V34:W34" si="31">U34</f>
         <v>e_w95343089-220</v>
       </c>
       <c r="W34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>e_w95343089-220</v>
       </c>
       <c r="X34" t="str">
@@ -3537,11 +3620,11 @@
         <v>125</v>
       </c>
       <c r="V35" t="str">
-        <f t="shared" ref="V35:W35" si="30">U35</f>
+        <f t="shared" ref="V35:W35" si="32">U35</f>
         <v>e_w95344674-220</v>
       </c>
       <c r="W35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>e_w95344674-220</v>
       </c>
       <c r="X35" t="str">
@@ -3590,11 +3673,11 @@
         <v>290</v>
       </c>
       <c r="V36" t="str">
-        <f t="shared" ref="V36:W36" si="31">U36</f>
+        <f t="shared" ref="V36:W36" si="33">U36</f>
         <v>e_w95512216-220</v>
       </c>
       <c r="W36" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>e_w95512216-220</v>
       </c>
       <c r="X36" t="str">
@@ -3643,11 +3726,11 @@
         <v>127</v>
       </c>
       <c r="V37" t="str">
-        <f t="shared" ref="V37:W37" si="32">U37</f>
+        <f t="shared" ref="V37:W37" si="34">U37</f>
         <v>e_w100957314-220</v>
       </c>
       <c r="W37" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>e_w100957314-220</v>
       </c>
       <c r="X37" t="str">
@@ -3696,11 +3779,11 @@
         <v>140</v>
       </c>
       <c r="V38" t="str">
-        <f t="shared" ref="V38:W38" si="33">U38</f>
+        <f t="shared" ref="V38:W38" si="35">U38</f>
         <v>e_w119877500-220</v>
       </c>
       <c r="W38" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>e_w119877500-220</v>
       </c>
       <c r="X38" t="str">
@@ -3749,11 +3832,11 @@
         <v>146</v>
       </c>
       <c r="V39" t="str">
-        <f t="shared" ref="V39:W39" si="34">U39</f>
+        <f t="shared" ref="V39:W39" si="36">U39</f>
         <v>e_w148300699-220</v>
       </c>
       <c r="W39" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>e_w148300699-220</v>
       </c>
       <c r="X39" t="str">
@@ -3802,11 +3885,11 @@
         <v>40</v>
       </c>
       <c r="V40" t="str">
-        <f t="shared" ref="V40:W40" si="35">U40</f>
+        <f t="shared" ref="V40:W40" si="37">U40</f>
         <v>e_w156094589-220</v>
       </c>
       <c r="W40" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>e_w156094589-220</v>
       </c>
       <c r="X40" t="str">
@@ -3855,11 +3938,11 @@
         <v>148</v>
       </c>
       <c r="V41" t="str">
-        <f t="shared" ref="V41:W41" si="36">U41</f>
+        <f t="shared" ref="V41:W41" si="38">U41</f>
         <v>e_w161270797-220</v>
       </c>
       <c r="W41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>e_w161270797-220</v>
       </c>
       <c r="X41" t="str">
@@ -3908,11 +3991,11 @@
         <v>114</v>
       </c>
       <c r="V42" t="str">
-        <f t="shared" ref="V42:W42" si="37">U42</f>
+        <f t="shared" ref="V42:W42" si="39">U42</f>
         <v>e_w167177413-220</v>
       </c>
       <c r="W42" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>e_w167177413-220</v>
       </c>
       <c r="X42" t="str">
@@ -3961,11 +4044,11 @@
         <v>24</v>
       </c>
       <c r="V43" t="str">
-        <f t="shared" ref="V43:W43" si="38">U43</f>
+        <f t="shared" ref="V43:W43" si="40">U43</f>
         <v>e_w167283894-220</v>
       </c>
       <c r="W43" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>e_w167283894-220</v>
       </c>
       <c r="X43" t="str">
@@ -4014,11 +4097,11 @@
         <v>132</v>
       </c>
       <c r="V44" t="str">
-        <f t="shared" ref="V44:W44" si="39">U44</f>
+        <f t="shared" ref="V44:W44" si="41">U44</f>
         <v>e_w167285260-220</v>
       </c>
       <c r="W44" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>e_w167285260-220</v>
       </c>
       <c r="X44" t="str">
@@ -4067,11 +4150,11 @@
         <v>51</v>
       </c>
       <c r="V45" t="str">
-        <f t="shared" ref="V45:W45" si="40">U45</f>
+        <f t="shared" ref="V45:W45" si="42">U45</f>
         <v>e_w167285336-220</v>
       </c>
       <c r="W45" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>e_w167285336-220</v>
       </c>
       <c r="X45" t="str">
@@ -4120,11 +4203,11 @@
         <v>73</v>
       </c>
       <c r="V46" t="str">
-        <f t="shared" ref="V46:W46" si="41">U46</f>
+        <f t="shared" ref="V46:W46" si="43">U46</f>
         <v>e_w167286837-220</v>
       </c>
       <c r="W46" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>e_w167286837-220</v>
       </c>
       <c r="X46" t="str">
@@ -4173,11 +4256,11 @@
         <v>116</v>
       </c>
       <c r="V47" t="str">
-        <f t="shared" ref="V47:W47" si="42">U47</f>
+        <f t="shared" ref="V47:W47" si="44">U47</f>
         <v>e_w167293888-220</v>
       </c>
       <c r="W47" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>e_w167293888-220</v>
       </c>
       <c r="X47" t="str">
@@ -4226,11 +4309,11 @@
         <v>165</v>
       </c>
       <c r="V48" t="str">
-        <f t="shared" ref="V48:W48" si="43">U48</f>
+        <f t="shared" ref="V48:W48" si="45">U48</f>
         <v>e_w167300914-220</v>
       </c>
       <c r="W48" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>e_w167300914-220</v>
       </c>
       <c r="X48" t="str">
@@ -4279,11 +4362,11 @@
         <v>123</v>
       </c>
       <c r="V49" t="str">
-        <f t="shared" ref="V49:W49" si="44">U49</f>
+        <f t="shared" ref="V49:W49" si="46">U49</f>
         <v>e_w167427251-220</v>
       </c>
       <c r="W49" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>e_w167427251-220</v>
       </c>
       <c r="X49" t="str">
@@ -4332,11 +4415,11 @@
         <v>171</v>
       </c>
       <c r="V50" t="str">
-        <f t="shared" ref="V50:W50" si="45">U50</f>
+        <f t="shared" ref="V50:W50" si="47">U50</f>
         <v>e_w167572576-220</v>
       </c>
       <c r="W50" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>e_w167572576-220</v>
       </c>
       <c r="X50" t="str">
@@ -4385,11 +4468,11 @@
         <v>58</v>
       </c>
       <c r="V51" t="str">
-        <f t="shared" ref="V51:W51" si="46">U51</f>
+        <f t="shared" ref="V51:W51" si="48">U51</f>
         <v>e_w167705537-220</v>
       </c>
       <c r="W51" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>e_w167705537-220</v>
       </c>
       <c r="X51" t="str">
@@ -4438,11 +4521,11 @@
         <v>174</v>
       </c>
       <c r="V52" t="str">
-        <f t="shared" ref="V52:W52" si="47">U52</f>
+        <f t="shared" ref="V52:W52" si="49">U52</f>
         <v>e_w169512273-220</v>
       </c>
       <c r="W52" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>e_w169512273-220</v>
       </c>
       <c r="X52" t="str">
@@ -4491,11 +4574,11 @@
         <v>76</v>
       </c>
       <c r="V53" t="str">
-        <f t="shared" ref="V53:W53" si="48">U53</f>
+        <f t="shared" ref="V53:W53" si="50">U53</f>
         <v>e_w170300247-220</v>
       </c>
       <c r="W53" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>e_w170300247-220</v>
       </c>
       <c r="X53" t="str">
@@ -4544,11 +4627,11 @@
         <v>96</v>
       </c>
       <c r="V54" t="str">
-        <f t="shared" ref="V54:W54" si="49">U54</f>
+        <f t="shared" ref="V54:W54" si="51">U54</f>
         <v>e_w180514007-220</v>
       </c>
       <c r="W54" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>e_w180514007-220</v>
       </c>
       <c r="X54" t="str">
@@ -4597,11 +4680,11 @@
         <v>98</v>
       </c>
       <c r="V55" t="str">
-        <f t="shared" ref="V55:W55" si="50">U55</f>
+        <f t="shared" ref="V55:W55" si="52">U55</f>
         <v>e_w180519027-220</v>
       </c>
       <c r="W55" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>e_w180519027-220</v>
       </c>
       <c r="X55" t="str">
@@ -4650,11 +4733,11 @@
         <v>120</v>
       </c>
       <c r="V56" t="str">
-        <f t="shared" ref="V56:W56" si="51">U56</f>
+        <f t="shared" ref="V56:W56" si="53">U56</f>
         <v>e_w187858674-220</v>
       </c>
       <c r="W56" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>e_w187858674-220</v>
       </c>
       <c r="X56" t="str">
@@ -4703,11 +4786,11 @@
         <v>184</v>
       </c>
       <c r="V57" t="str">
-        <f t="shared" ref="V57:W57" si="52">U57</f>
+        <f t="shared" ref="V57:W57" si="54">U57</f>
         <v>e_w191346761-220</v>
       </c>
       <c r="W57" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>e_w191346761-220</v>
       </c>
       <c r="X57" t="str">
@@ -4756,11 +4839,11 @@
         <v>236</v>
       </c>
       <c r="V58" t="str">
-        <f t="shared" ref="V58:W58" si="53">U58</f>
+        <f t="shared" ref="V58:W58" si="55">U58</f>
         <v>e_w232382576-220</v>
       </c>
       <c r="W58" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>e_w232382576-220</v>
       </c>
       <c r="X58" t="str">
@@ -4809,11 +4892,11 @@
         <v>91</v>
       </c>
       <c r="V59" t="str">
-        <f t="shared" ref="V59:W59" si="54">U59</f>
+        <f t="shared" ref="V59:W59" si="56">U59</f>
         <v>e_w235066414-220</v>
       </c>
       <c r="W59" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>e_w235066414-220</v>
       </c>
       <c r="X59" t="str">
@@ -4862,11 +4945,11 @@
         <v>203</v>
       </c>
       <c r="V60" t="str">
-        <f t="shared" ref="V60:W60" si="55">U60</f>
+        <f t="shared" ref="V60:W60" si="57">U60</f>
         <v>e_w255873374-220</v>
       </c>
       <c r="W60" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>e_w255873374-220</v>
       </c>
       <c r="X60" t="str">
@@ -4915,11 +4998,11 @@
         <v>63</v>
       </c>
       <c r="V61" t="str">
-        <f t="shared" ref="V61:W61" si="56">U61</f>
+        <f t="shared" ref="V61:W61" si="58">U61</f>
         <v>e_w268826084-220</v>
       </c>
       <c r="W61" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>e_w268826084-220</v>
       </c>
       <c r="X61" t="str">
@@ -4968,11 +5051,11 @@
         <v>101</v>
       </c>
       <c r="V62" t="str">
-        <f t="shared" ref="V62:W62" si="57">U62</f>
+        <f t="shared" ref="V62:W62" si="59">U62</f>
         <v>e_w268841395-220</v>
       </c>
       <c r="W62" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>e_w268841395-220</v>
       </c>
       <c r="X62" t="str">
@@ -5021,11 +5104,11 @@
         <v>67</v>
       </c>
       <c r="V63" t="str">
-        <f t="shared" ref="V63:W63" si="58">U63</f>
+        <f t="shared" ref="V63:W63" si="60">U63</f>
         <v>e_w270012796-220</v>
       </c>
       <c r="W63" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>e_w270012796-220</v>
       </c>
       <c r="X63" t="str">
@@ -5074,11 +5157,11 @@
         <v>157</v>
       </c>
       <c r="V64" t="str">
-        <f t="shared" ref="V64:W64" si="59">U64</f>
+        <f t="shared" ref="V64:W64" si="61">U64</f>
         <v>e_w270018358-220</v>
       </c>
       <c r="W64" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>e_w270018358-220</v>
       </c>
       <c r="X64" t="str">
@@ -5127,11 +5210,11 @@
         <v>141</v>
       </c>
       <c r="V65" t="str">
-        <f t="shared" ref="V65:W65" si="60">U65</f>
+        <f t="shared" ref="V65:W65" si="62">U65</f>
         <v>e_w270022030-220</v>
       </c>
       <c r="W65" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>e_w270022030-220</v>
       </c>
       <c r="X65" t="str">
@@ -5180,11 +5263,11 @@
         <v>159</v>
       </c>
       <c r="V66" t="str">
-        <f t="shared" ref="V66:W66" si="61">U66</f>
+        <f t="shared" ref="V66:W66" si="63">U66</f>
         <v>e_w270554679-220</v>
       </c>
       <c r="W66" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>e_w270554679-220</v>
       </c>
       <c r="X66" t="str">
@@ -5233,11 +5316,11 @@
         <v>205</v>
       </c>
       <c r="V67" t="str">
-        <f t="shared" ref="V67:W67" si="62">U67</f>
+        <f t="shared" ref="V67:W67" si="64">U67</f>
         <v>e_w270556206-220</v>
       </c>
       <c r="W67" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>e_w270556206-220</v>
       </c>
       <c r="X67" t="str">
@@ -5286,11 +5369,11 @@
         <v>107</v>
       </c>
       <c r="V68" t="str">
-        <f t="shared" ref="V68:W68" si="63">U68</f>
+        <f t="shared" ref="V68:W68" si="65">U68</f>
         <v>e_w272195826-220</v>
       </c>
       <c r="W68" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>e_w272195826-220</v>
       </c>
       <c r="X68" t="str">
@@ -5339,11 +5422,11 @@
         <v>208</v>
       </c>
       <c r="V69" t="str">
-        <f t="shared" ref="V69:W69" si="64">U69</f>
+        <f t="shared" ref="V69:W69" si="66">U69</f>
         <v>e_w272522517-220</v>
       </c>
       <c r="W69" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>e_w272522517-220</v>
       </c>
       <c r="X69" t="str">
@@ -5392,15 +5475,15 @@
         <v>27</v>
       </c>
       <c r="V70" t="str">
-        <f t="shared" ref="V70:W70" si="65">U70</f>
+        <f t="shared" ref="V70:W70" si="67">U70</f>
         <v>e_w275188676-220</v>
       </c>
       <c r="W70" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>e_w275188676-220</v>
       </c>
       <c r="X70" t="str">
-        <f t="shared" ref="X70:X128" si="66">"TU_"&amp;U70</f>
+        <f t="shared" ref="X70:X128" si="68">"TU_"&amp;U70</f>
         <v>TU_e_w275188676-220</v>
       </c>
       <c r="Y70" t="s">
@@ -5445,15 +5528,15 @@
         <v>219</v>
       </c>
       <c r="V71" t="str">
-        <f t="shared" ref="V71:W71" si="67">U71</f>
+        <f t="shared" ref="V71:W71" si="69">U71</f>
         <v>e_w341099346-220</v>
       </c>
       <c r="W71" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>e_w341099346-220</v>
       </c>
       <c r="X71" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w341099346-220</v>
       </c>
       <c r="Y71" t="s">
@@ -5498,15 +5581,15 @@
         <v>223</v>
       </c>
       <c r="V72" t="str">
-        <f t="shared" ref="V72:W72" si="68">U72</f>
+        <f t="shared" ref="V72:W72" si="70">U72</f>
         <v>e_w359449581-220</v>
       </c>
       <c r="W72" t="str">
+        <f t="shared" si="70"/>
+        <v>e_w359449581-220</v>
+      </c>
+      <c r="X72" t="str">
         <f t="shared" si="68"/>
-        <v>e_w359449581-220</v>
-      </c>
-      <c r="X72" t="str">
-        <f t="shared" si="66"/>
         <v>TU_e_w359449581-220</v>
       </c>
       <c r="Y72" t="s">
@@ -5551,15 +5634,15 @@
         <v>226</v>
       </c>
       <c r="V73" t="str">
-        <f t="shared" ref="V73:W73" si="69">U73</f>
+        <f t="shared" ref="V73:W73" si="71">U73</f>
         <v>e_w409049317-220</v>
       </c>
       <c r="W73" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>e_w409049317-220</v>
       </c>
       <c r="X73" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w409049317-220</v>
       </c>
       <c r="Y73" t="s">
@@ -5604,15 +5687,15 @@
         <v>230</v>
       </c>
       <c r="V74" t="str">
-        <f t="shared" ref="V74:W74" si="70">U74</f>
+        <f t="shared" ref="V74:W74" si="72">U74</f>
         <v>e_w412589726-220</v>
       </c>
       <c r="W74" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="72"/>
         <v>e_w412589726-220</v>
       </c>
       <c r="X74" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w412589726-220</v>
       </c>
       <c r="Y74" t="s">
@@ -5657,15 +5740,15 @@
         <v>181</v>
       </c>
       <c r="V75" t="str">
-        <f t="shared" ref="V75:W75" si="71">U75</f>
+        <f t="shared" ref="V75:W75" si="73">U75</f>
         <v>e_w414953388-220</v>
       </c>
       <c r="W75" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>e_w414953388-220</v>
       </c>
       <c r="X75" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w414953388-220</v>
       </c>
       <c r="Y75" t="s">
@@ -5710,15 +5793,15 @@
         <v>238</v>
       </c>
       <c r="V76" t="str">
-        <f t="shared" ref="V76:W76" si="72">U76</f>
+        <f t="shared" ref="V76:W76" si="74">U76</f>
         <v>e_w627162826-220</v>
       </c>
       <c r="W76" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>e_w627162826-220</v>
       </c>
       <c r="X76" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w627162826-220</v>
       </c>
       <c r="Y76" t="s">
@@ -5763,15 +5846,15 @@
         <v>242</v>
       </c>
       <c r="V77" t="str">
-        <f t="shared" ref="V77:W77" si="73">U77</f>
+        <f t="shared" ref="V77:W77" si="75">U77</f>
         <v>e_w849110529-220</v>
       </c>
       <c r="W77" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="75"/>
         <v>e_w849110529-220</v>
       </c>
       <c r="X77" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w849110529-220</v>
       </c>
       <c r="Y77" t="s">
@@ -5816,15 +5899,15 @@
         <v>144</v>
       </c>
       <c r="V78" t="str">
-        <f t="shared" ref="V78:W78" si="74">U78</f>
+        <f t="shared" ref="V78:W78" si="76">U78</f>
         <v>e_w907631032-220</v>
       </c>
       <c r="W78" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="76"/>
         <v>e_w907631032-220</v>
       </c>
       <c r="X78" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w907631032-220</v>
       </c>
       <c r="Y78" t="s">
@@ -5869,15 +5952,15 @@
         <v>129</v>
       </c>
       <c r="V79" t="str">
-        <f t="shared" ref="V79:W79" si="75">U79</f>
+        <f t="shared" ref="V79:W79" si="77">U79</f>
         <v>e_w1018655038-220</v>
       </c>
       <c r="W79" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="77"/>
         <v>e_w1018655038-220</v>
       </c>
       <c r="X79" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w1018655038-220</v>
       </c>
       <c r="Y79" t="s">
@@ -5922,15 +6005,15 @@
         <v>138</v>
       </c>
       <c r="V80" t="str">
-        <f t="shared" ref="V80:W80" si="76">U80</f>
+        <f t="shared" ref="V80:W80" si="78">U80</f>
         <v>e_w1026587442-220</v>
       </c>
       <c r="W80" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="78"/>
         <v>e_w1026587442-220</v>
       </c>
       <c r="X80" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w1026587442-220</v>
       </c>
       <c r="Y80" t="s">
@@ -5975,15 +6058,15 @@
         <v>30</v>
       </c>
       <c r="V81" t="str">
-        <f t="shared" ref="V81:W81" si="77">U81</f>
+        <f t="shared" ref="V81:W81" si="79">U81</f>
         <v>e_w1034927052-220</v>
       </c>
       <c r="W81" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>e_w1034927052-220</v>
       </c>
       <c r="X81" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w1034927052-220</v>
       </c>
       <c r="Y81" t="s">
@@ -6028,15 +6111,15 @@
         <v>134</v>
       </c>
       <c r="V82" t="str">
-        <f t="shared" ref="V82:W82" si="78">U82</f>
+        <f t="shared" ref="V82:W82" si="80">U82</f>
         <v>e_w1099619174-220</v>
       </c>
       <c r="W82" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>e_w1099619174-220</v>
       </c>
       <c r="X82" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w1099619174-220</v>
       </c>
       <c r="Y82" t="s">
@@ -6081,15 +6164,15 @@
         <v>137</v>
       </c>
       <c r="V83" t="str">
-        <f t="shared" ref="V83:W83" si="79">U83</f>
+        <f t="shared" ref="V83:W83" si="81">U83</f>
         <v>e_w1167708390-220</v>
       </c>
       <c r="W83" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>e_w1167708390-220</v>
       </c>
       <c r="X83" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w1167708390-220</v>
       </c>
       <c r="Y83" t="s">
@@ -6134,15 +6217,15 @@
         <v>143</v>
       </c>
       <c r="V84" t="str">
-        <f t="shared" ref="V84:W84" si="80">U84</f>
+        <f t="shared" ref="V84:W84" si="82">U84</f>
         <v>e_w1363994055-220</v>
       </c>
       <c r="W84" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>e_w1363994055-220</v>
       </c>
       <c r="X84" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_w1363994055-220</v>
       </c>
       <c r="Y84" t="s">
@@ -6187,15 +6270,15 @@
         <v>122</v>
       </c>
       <c r="V85" t="str">
-        <f t="shared" ref="V85:W85" si="81">U85</f>
+        <f t="shared" ref="V85:W85" si="83">U85</f>
         <v>e_r17609399-220</v>
       </c>
       <c r="W85" t="str">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>e_r17609399-220</v>
       </c>
       <c r="X85" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_r17609399-220</v>
       </c>
       <c r="Y85" t="s">
@@ -6240,15 +6323,15 @@
         <v>55</v>
       </c>
       <c r="V86" t="str">
-        <f t="shared" ref="V86:W86" si="82">U86</f>
+        <f t="shared" ref="V86:W86" si="84">U86</f>
         <v>e_NZ26-220</v>
       </c>
       <c r="W86" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>e_NZ26-220</v>
       </c>
       <c r="X86" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ26-220</v>
       </c>
       <c r="Y86" t="s">
@@ -6293,15 +6376,15 @@
         <v>60</v>
       </c>
       <c r="V87" t="str">
-        <f t="shared" ref="V87:W87" si="83">U87</f>
+        <f t="shared" ref="V87:W87" si="85">U87</f>
         <v>e_NZ28-220</v>
       </c>
       <c r="W87" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>e_NZ28-220</v>
       </c>
       <c r="X87" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ28-220</v>
       </c>
       <c r="Y87" t="s">
@@ -6346,15 +6429,15 @@
         <v>90</v>
       </c>
       <c r="V88" t="str">
-        <f t="shared" ref="V88:W88" si="84">U88</f>
+        <f t="shared" ref="V88:W88" si="86">U88</f>
         <v>e_NZ4-220</v>
       </c>
       <c r="W88" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>e_NZ4-220</v>
       </c>
       <c r="X88" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ4-220</v>
       </c>
       <c r="Y88" t="s">
@@ -6399,15 +6482,15 @@
         <v>42</v>
       </c>
       <c r="V89" t="str">
-        <f t="shared" ref="V89:W89" si="85">U89</f>
+        <f t="shared" ref="V89:W89" si="87">U89</f>
         <v>e_NZ20-220</v>
       </c>
       <c r="W89" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>e_NZ20-220</v>
       </c>
       <c r="X89" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ20-220</v>
       </c>
       <c r="Y89" t="s">
@@ -6452,15 +6535,15 @@
         <v>35</v>
       </c>
       <c r="V90" t="str">
-        <f t="shared" ref="V90:W90" si="86">U90</f>
+        <f t="shared" ref="V90:W90" si="88">U90</f>
         <v>e_NZ19-220</v>
       </c>
       <c r="W90" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>e_NZ19-220</v>
       </c>
       <c r="X90" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ19-220</v>
       </c>
       <c r="Y90" t="s">
@@ -6505,15 +6588,15 @@
         <v>81</v>
       </c>
       <c r="V91" t="str">
-        <f t="shared" ref="V91:W91" si="87">U91</f>
+        <f t="shared" ref="V91:W91" si="89">U91</f>
         <v>e_NZ37-220</v>
       </c>
       <c r="W91" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>e_NZ37-220</v>
       </c>
       <c r="X91" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ37-220</v>
       </c>
       <c r="Y91" t="s">
@@ -6558,15 +6641,15 @@
         <v>80</v>
       </c>
       <c r="V92" t="str">
-        <f t="shared" ref="V92:W92" si="88">U92</f>
+        <f t="shared" ref="V92:W92" si="90">U92</f>
         <v>e_NZ36-220</v>
       </c>
       <c r="W92" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>e_NZ36-220</v>
       </c>
       <c r="X92" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ36-220</v>
       </c>
       <c r="Y92" t="s">
@@ -6611,15 +6694,15 @@
         <v>70</v>
       </c>
       <c r="V93" t="str">
-        <f t="shared" ref="V93:W93" si="89">U93</f>
+        <f t="shared" ref="V93:W93" si="91">U93</f>
         <v>e_NZ34-220</v>
       </c>
       <c r="W93" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>e_NZ34-220</v>
       </c>
       <c r="X93" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ34-220</v>
       </c>
       <c r="Y93" t="s">
@@ -6664,15 +6747,15 @@
         <v>87</v>
       </c>
       <c r="V94" t="str">
-        <f t="shared" ref="V94:W94" si="90">U94</f>
+        <f t="shared" ref="V94:W94" si="92">U94</f>
         <v>e_NZ39-220</v>
       </c>
       <c r="W94" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>e_NZ39-220</v>
       </c>
       <c r="X94" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ39-220</v>
       </c>
       <c r="Y94" t="s">
@@ -6717,15 +6800,15 @@
         <v>61</v>
       </c>
       <c r="V95" t="str">
-        <f t="shared" ref="V95:W95" si="91">U95</f>
+        <f t="shared" ref="V95:W95" si="93">U95</f>
         <v>e_NZ29-220</v>
       </c>
       <c r="W95" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>e_NZ29-220</v>
       </c>
       <c r="X95" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ29-220</v>
       </c>
       <c r="Y95" t="s">
@@ -6770,15 +6853,15 @@
         <v>103</v>
       </c>
       <c r="V96" t="str">
-        <f t="shared" ref="V96:W96" si="92">U96</f>
+        <f t="shared" ref="V96:W96" si="94">U96</f>
         <v>e_NZ42-220</v>
       </c>
       <c r="W96" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>e_NZ42-220</v>
       </c>
       <c r="X96" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ42-220</v>
       </c>
       <c r="Y96" t="s">
@@ -6823,15 +6906,15 @@
         <v>100</v>
       </c>
       <c r="V97" t="str">
-        <f t="shared" ref="V97:W97" si="93">U97</f>
+        <f t="shared" ref="V97:W97" si="95">U97</f>
         <v>e_NZ41-220</v>
       </c>
       <c r="W97" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>e_NZ41-220</v>
       </c>
       <c r="X97" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ41-220</v>
       </c>
       <c r="Y97" t="s">
@@ -6876,15 +6959,15 @@
         <v>106</v>
       </c>
       <c r="V98" t="str">
-        <f t="shared" ref="V98:W98" si="94">U98</f>
+        <f t="shared" ref="V98:W98" si="96">U98</f>
         <v>e_NZ43-220</v>
       </c>
       <c r="W98" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>e_NZ43-220</v>
       </c>
       <c r="X98" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ43-220</v>
       </c>
       <c r="Y98" t="s">
@@ -6929,15 +7012,15 @@
         <v>14</v>
       </c>
       <c r="V99" t="str">
-        <f t="shared" ref="V99:W99" si="95">U99</f>
+        <f t="shared" ref="V99:W99" si="97">U99</f>
         <v>e_NZ10-220</v>
       </c>
       <c r="W99" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>e_NZ10-220</v>
       </c>
       <c r="X99" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ10-220</v>
       </c>
       <c r="Y99" t="s">
@@ -6982,15 +7065,15 @@
         <v>47</v>
       </c>
       <c r="V100" t="str">
-        <f t="shared" ref="V100:W100" si="96">U100</f>
+        <f t="shared" ref="V100:W100" si="98">U100</f>
         <v>e_NZ21-220</v>
       </c>
       <c r="W100" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>e_NZ21-220</v>
       </c>
       <c r="X100" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ21-220</v>
       </c>
       <c r="Y100" t="s">
@@ -7035,15 +7118,15 @@
         <v>26</v>
       </c>
       <c r="V101" t="str">
-        <f t="shared" ref="V101:W101" si="97">U101</f>
+        <f t="shared" ref="V101:W101" si="99">U101</f>
         <v>e_NZ16-220</v>
       </c>
       <c r="W101" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>e_NZ16-220</v>
       </c>
       <c r="X101" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ16-220</v>
       </c>
       <c r="Y101" t="s">
@@ -7088,15 +7171,15 @@
         <v>72</v>
       </c>
       <c r="V102" t="str">
-        <f t="shared" ref="V102:W102" si="98">U102</f>
+        <f t="shared" ref="V102:W102" si="100">U102</f>
         <v>e_NZ32-220</v>
       </c>
       <c r="W102" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="100"/>
         <v>e_NZ32-220</v>
       </c>
       <c r="X102" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ32-220</v>
       </c>
       <c r="Y102" t="s">
@@ -7141,15 +7224,15 @@
         <v>113</v>
       </c>
       <c r="V103" t="str">
-        <f t="shared" ref="V103:W103" si="99">U103</f>
+        <f t="shared" ref="V103:W103" si="101">U103</f>
         <v>e_NZ7-220</v>
       </c>
       <c r="W103" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="101"/>
         <v>e_NZ7-220</v>
       </c>
       <c r="X103" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ7-220</v>
       </c>
       <c r="Y103" t="s">
@@ -7194,15 +7277,15 @@
         <v>53</v>
       </c>
       <c r="V104" t="str">
-        <f t="shared" ref="V104:W104" si="100">U104</f>
+        <f t="shared" ref="V104:W104" si="102">U104</f>
         <v>e_NZ25-220</v>
       </c>
       <c r="W104" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="102"/>
         <v>e_NZ25-220</v>
       </c>
       <c r="X104" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ25-220</v>
       </c>
       <c r="Y104" t="s">
@@ -7247,15 +7330,15 @@
         <v>50</v>
       </c>
       <c r="V105" t="str">
-        <f t="shared" ref="V105:W105" si="101">U105</f>
+        <f t="shared" ref="V105:W105" si="103">U105</f>
         <v>e_NZ24-220</v>
       </c>
       <c r="W105" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="103"/>
         <v>e_NZ24-220</v>
       </c>
       <c r="X105" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ24-220</v>
       </c>
       <c r="Y105" t="s">
@@ -7300,15 +7383,15 @@
         <v>95</v>
       </c>
       <c r="V106" t="str">
-        <f t="shared" ref="V106:W106" si="102">U106</f>
+        <f t="shared" ref="V106:W106" si="104">U106</f>
         <v>e_NZ40-220</v>
       </c>
       <c r="W106" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="104"/>
         <v>e_NZ40-220</v>
       </c>
       <c r="X106" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ40-220</v>
       </c>
       <c r="Y106" t="s">
@@ -7353,15 +7436,15 @@
         <v>118</v>
       </c>
       <c r="V107" t="str">
-        <f t="shared" ref="V107:W107" si="103">U107</f>
+        <f t="shared" ref="V107:W107" si="105">U107</f>
         <v>e_NZ9-220</v>
       </c>
       <c r="W107" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="105"/>
         <v>e_NZ9-220</v>
       </c>
       <c r="X107" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ9-220</v>
       </c>
       <c r="Y107" t="s">
@@ -7406,15 +7489,15 @@
         <v>17</v>
       </c>
       <c r="V108" t="str">
-        <f t="shared" ref="V108:W108" si="104">U108</f>
+        <f t="shared" ref="V108:W108" si="106">U108</f>
         <v>e_NZ11-220</v>
       </c>
       <c r="W108" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="106"/>
         <v>e_NZ11-220</v>
       </c>
       <c r="X108" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ11-220</v>
       </c>
       <c r="Y108" t="s">
@@ -7459,15 +7542,15 @@
         <v>18</v>
       </c>
       <c r="V109" t="str">
-        <f t="shared" ref="V109:W109" si="105">U109</f>
+        <f t="shared" ref="V109:W109" si="107">U109</f>
         <v>e_NZ12-220</v>
       </c>
       <c r="W109" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="107"/>
         <v>e_NZ12-220</v>
       </c>
       <c r="X109" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ12-220</v>
       </c>
       <c r="Y109" t="s">
@@ -7512,15 +7595,15 @@
         <v>57</v>
       </c>
       <c r="V110" t="str">
-        <f t="shared" ref="V110:W110" si="106">U110</f>
+        <f t="shared" ref="V110:W110" si="108">U110</f>
         <v>e_NZ27-220</v>
       </c>
       <c r="W110" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="108"/>
         <v>e_NZ27-220</v>
       </c>
       <c r="X110" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ27-220</v>
       </c>
       <c r="Y110" t="s">
@@ -7565,15 +7648,15 @@
         <v>109</v>
       </c>
       <c r="V111" t="str">
-        <f t="shared" ref="V111:W111" si="107">U111</f>
+        <f t="shared" ref="V111:W111" si="109">U111</f>
         <v>e_NZ5-220</v>
       </c>
       <c r="W111" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="109"/>
         <v>e_NZ5-220</v>
       </c>
       <c r="X111" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ5-220</v>
       </c>
       <c r="Y111" t="s">
@@ -7618,15 +7701,15 @@
         <v>37</v>
       </c>
       <c r="V112" t="str">
-        <f t="shared" ref="V112:W112" si="108">U112</f>
+        <f t="shared" ref="V112:W112" si="110">U112</f>
         <v>e_NZ2-220</v>
       </c>
       <c r="W112" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="110"/>
         <v>e_NZ2-220</v>
       </c>
       <c r="X112" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ2-220</v>
       </c>
       <c r="Y112" t="s">
@@ -7671,15 +7754,15 @@
         <v>38</v>
       </c>
       <c r="V113" t="str">
-        <f t="shared" ref="V113:W113" si="109">U113</f>
+        <f t="shared" ref="V113:W113" si="111">U113</f>
         <v>e_NZ3-220</v>
       </c>
       <c r="W113" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="111"/>
         <v>e_NZ3-220</v>
       </c>
       <c r="X113" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ3-220</v>
       </c>
       <c r="Y113" t="s">
@@ -7724,15 +7807,15 @@
         <v>32</v>
       </c>
       <c r="V114" t="str">
-        <f t="shared" ref="V114:W114" si="110">U114</f>
+        <f t="shared" ref="V114:W114" si="112">U114</f>
         <v>e_NZ18-220</v>
       </c>
       <c r="W114" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="112"/>
         <v>e_NZ18-220</v>
       </c>
       <c r="X114" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ18-220</v>
       </c>
       <c r="Y114" t="s">
@@ -7777,15 +7860,15 @@
         <v>20</v>
       </c>
       <c r="V115" t="str">
-        <f t="shared" ref="V115:W115" si="111">U115</f>
+        <f t="shared" ref="V115:W115" si="113">U115</f>
         <v>e_NZ6-220</v>
       </c>
       <c r="W115" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="113"/>
         <v>e_NZ6-220</v>
       </c>
       <c r="X115" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ6-220</v>
       </c>
       <c r="Y115" t="s">
@@ -7830,15 +7913,15 @@
         <v>66</v>
       </c>
       <c r="V116" t="str">
-        <f t="shared" ref="V116:W116" si="112">U116</f>
+        <f t="shared" ref="V116:W116" si="114">U116</f>
         <v>e_NZ30-220</v>
       </c>
       <c r="W116" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="114"/>
         <v>e_NZ30-220</v>
       </c>
       <c r="X116" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ30-220</v>
       </c>
       <c r="Y116" t="s">
@@ -7883,15 +7966,15 @@
         <v>10</v>
       </c>
       <c r="V117" t="str">
-        <f t="shared" ref="V117:W117" si="113">U117</f>
+        <f t="shared" ref="V117:W117" si="115">U117</f>
         <v>e_NZ1-220</v>
       </c>
       <c r="W117" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="115"/>
         <v>e_NZ1-220</v>
       </c>
       <c r="X117" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ1-220</v>
       </c>
       <c r="Y117" t="s">
@@ -7936,15 +8019,15 @@
         <v>29</v>
       </c>
       <c r="V118" t="str">
-        <f t="shared" ref="V118:W118" si="114">U118</f>
+        <f t="shared" ref="V118:W118" si="116">U118</f>
         <v>e_NZ17-220</v>
       </c>
       <c r="W118" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="116"/>
         <v>e_NZ17-220</v>
       </c>
       <c r="X118" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ17-220</v>
       </c>
       <c r="Y118" t="s">
@@ -7989,15 +8072,15 @@
         <v>43</v>
       </c>
       <c r="V119" t="str">
-        <f t="shared" ref="V119:W119" si="115">U119</f>
+        <f t="shared" ref="V119:W119" si="117">U119</f>
         <v>e_NZ22-220</v>
       </c>
       <c r="W119" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="117"/>
         <v>e_NZ22-220</v>
       </c>
       <c r="X119" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ22-220</v>
       </c>
       <c r="Y119" t="s">
@@ -8042,15 +8125,15 @@
         <v>69</v>
       </c>
       <c r="V120" t="str">
-        <f t="shared" ref="V120:W120" si="116">U120</f>
+        <f t="shared" ref="V120:W120" si="118">U120</f>
         <v>e_NZ31-220</v>
       </c>
       <c r="W120" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="118"/>
         <v>e_NZ31-220</v>
       </c>
       <c r="X120" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ31-220</v>
       </c>
       <c r="Y120" t="s">
@@ -8095,15 +8178,15 @@
         <v>23</v>
       </c>
       <c r="V121" t="str">
-        <f t="shared" ref="V121:W121" si="117">U121</f>
+        <f t="shared" ref="V121:W121" si="119">U121</f>
         <v>e_NZ13-220</v>
       </c>
       <c r="W121" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="119"/>
         <v>e_NZ13-220</v>
       </c>
       <c r="X121" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ13-220</v>
       </c>
       <c r="Y121" t="s">
@@ -8148,15 +8231,15 @@
         <v>247</v>
       </c>
       <c r="V122" t="str">
-        <f t="shared" ref="V122:W122" si="118">U122</f>
+        <f t="shared" ref="V122:W122" si="120">U122</f>
         <v>e_NZ14-220</v>
       </c>
       <c r="W122" t="str">
-        <f t="shared" si="118"/>
+        <f t="shared" si="120"/>
         <v>e_NZ14-220</v>
       </c>
       <c r="X122" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ14-220</v>
       </c>
       <c r="Y122" t="s">
@@ -8201,15 +8284,15 @@
         <v>45</v>
       </c>
       <c r="V123" t="str">
-        <f t="shared" ref="V123:W123" si="119">U123</f>
+        <f t="shared" ref="V123:W123" si="121">U123</f>
         <v>e_NZ23-220</v>
       </c>
       <c r="W123" t="str">
-        <f t="shared" si="119"/>
+        <f t="shared" si="121"/>
         <v>e_NZ23-220</v>
       </c>
       <c r="X123" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ23-220</v>
       </c>
       <c r="Y123" t="s">
@@ -8254,15 +8337,15 @@
         <v>265</v>
       </c>
       <c r="V124" t="str">
-        <f t="shared" ref="V124:W124" si="120">U124</f>
+        <f t="shared" ref="V124:W124" si="122">U124</f>
         <v>e_NZ38-220</v>
       </c>
       <c r="W124" t="str">
-        <f t="shared" si="120"/>
+        <f t="shared" si="122"/>
         <v>e_NZ38-220</v>
       </c>
       <c r="X124" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ38-220</v>
       </c>
       <c r="Y124" t="s">
@@ -8307,15 +8390,15 @@
         <v>15</v>
       </c>
       <c r="V125" t="str">
-        <f t="shared" ref="V125:W125" si="121">U125</f>
+        <f t="shared" ref="V125:W125" si="123">U125</f>
         <v>e_NZ8-220</v>
       </c>
       <c r="W125" t="str">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>e_NZ8-220</v>
       </c>
       <c r="X125" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ8-220</v>
       </c>
       <c r="Y125" t="s">
@@ -8360,15 +8443,15 @@
         <v>256</v>
       </c>
       <c r="V126" t="str">
-        <f t="shared" ref="V126:W126" si="122">U126</f>
+        <f t="shared" ref="V126:W126" si="124">U126</f>
         <v>e_NZ35-220</v>
       </c>
       <c r="W126" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>e_NZ35-220</v>
       </c>
       <c r="X126" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ35-220</v>
       </c>
       <c r="Y126" t="s">
@@ -8413,15 +8496,15 @@
         <v>261</v>
       </c>
       <c r="V127" t="str">
-        <f t="shared" ref="V127:W127" si="123">U127</f>
+        <f t="shared" ref="V127:W127" si="125">U127</f>
         <v>e_NZ33-220</v>
       </c>
       <c r="W127" t="str">
-        <f t="shared" si="123"/>
+        <f t="shared" si="125"/>
         <v>e_NZ33-220</v>
       </c>
       <c r="X127" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ33-220</v>
       </c>
       <c r="Y127" t="s">
@@ -8466,15 +8549,15 @@
         <v>154</v>
       </c>
       <c r="V128" t="str">
-        <f t="shared" ref="V128:W128" si="124">U128</f>
+        <f t="shared" ref="V128:W128" si="126">U128</f>
         <v>e_NZ15-220</v>
       </c>
       <c r="W128" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="126"/>
         <v>e_NZ15-220</v>
       </c>
       <c r="X128" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>TU_e_NZ15-220</v>
       </c>
       <c r="Y128" t="s">

--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04DD684-02DE-42D1-99D4-42F269C4C48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6E497A-ABB9-4C3C-95EB-09FA44C38E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
@@ -1291,7 +1291,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1328,6 +1328,14 @@
       <b/>
       <sz val="10"/>
       <color indexed="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1388,7 +1396,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1407,6 +1415,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3560,8 +3569,8 @@
       <c r="S34" t="s">
         <v>8</v>
       </c>
-      <c r="T34" t="s">
-        <v>393</v>
+      <c r="T34" s="8" t="s">
+        <v>394</v>
       </c>
       <c r="U34" t="s">
         <v>279</v>
@@ -9494,6 +9503,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6E497A-ABB9-4C3C-95EB-09FA44C38E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8D6DF6-0331-4D9F-A330-8E12355DCD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{EA63F65C-5A3D-417C-8323-0FC05D450A30}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="420">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -1285,6 +1285,18 @@
   </si>
   <si>
     <t>WOD</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>HYD</t>
   </si>
 </sst>
 </file>
@@ -1773,9 +1785,6 @@
       <c r="S3" t="s">
         <v>0</v>
       </c>
-      <c r="AA3" t="s">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
@@ -1826,27 +1835,6 @@
       <c r="Y4" t="s">
         <v>7</v>
       </c>
-      <c r="AA4" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="5" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
@@ -1900,29 +1888,6 @@
       <c r="Y5" t="s">
         <v>395</v>
       </c>
-      <c r="AA5" t="s">
-        <v>393</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>396</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>397</v>
-      </c>
-      <c r="AE5" t="str">
-        <f>AC5</f>
-        <v>gas</v>
-      </c>
-      <c r="AF5" t="str">
-        <f>"TU_"&amp;AD5</f>
-        <v>TU_ELCNGA</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="6" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
@@ -1976,29 +1941,6 @@
       <c r="Y6" t="s">
         <v>395</v>
       </c>
-      <c r="AA6" t="s">
-        <v>393</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>412</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>405</v>
-      </c>
-      <c r="AE6" t="str">
-        <f>AC6</f>
-        <v>coal</v>
-      </c>
-      <c r="AF6" t="str">
-        <f>"TU_ELC"&amp;AD6</f>
-        <v>TU_ELCCOA</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="7" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
@@ -2052,29 +1994,6 @@
       <c r="Y7" t="s">
         <v>395</v>
       </c>
-      <c r="AA7" t="s">
-        <v>393</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>413</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>401</v>
-      </c>
-      <c r="AE7" t="str">
-        <f t="shared" ref="AE7:AE8" si="3">AC7</f>
-        <v>oil</v>
-      </c>
-      <c r="AF7" t="str">
-        <f t="shared" ref="AF7:AF8" si="4">"TU_ELC"&amp;AD7</f>
-        <v>TU_ELCDSL</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
@@ -2114,11 +2033,11 @@
         <v>192</v>
       </c>
       <c r="V8" t="str">
-        <f t="shared" ref="V8:W8" si="5">U8</f>
+        <f t="shared" ref="V8:W8" si="3">U8</f>
         <v>e_w61853727-220</v>
       </c>
       <c r="W8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>e_w61853727-220</v>
       </c>
       <c r="X8" t="str">
@@ -2128,29 +2047,6 @@
       <c r="Y8" t="s">
         <v>395</v>
       </c>
-      <c r="AA8" t="s">
-        <v>393</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>414</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>415</v>
-      </c>
-      <c r="AE8" t="str">
-        <f t="shared" si="3"/>
-        <v>bioenergy</v>
-      </c>
-      <c r="AF8" t="str">
-        <f t="shared" si="4"/>
-        <v>TU_ELCWOD</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="9" spans="2:37" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
@@ -2190,11 +2086,11 @@
         <v>221</v>
       </c>
       <c r="V9" t="str">
-        <f t="shared" ref="V9:W9" si="6">U9</f>
+        <f t="shared" ref="V9:W9" si="4">U9</f>
         <v>e_w75609279-220</v>
       </c>
       <c r="W9" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>e_w75609279-220</v>
       </c>
       <c r="X9" t="str">
@@ -2243,11 +2139,11 @@
         <v>150</v>
       </c>
       <c r="V10" t="str">
-        <f t="shared" ref="V10:W10" si="7">U10</f>
+        <f t="shared" ref="V10:W10" si="5">U10</f>
         <v>e_w82881422-220</v>
       </c>
       <c r="W10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>e_w82881422-220</v>
       </c>
       <c r="X10" t="str">
@@ -2296,11 +2192,11 @@
         <v>130</v>
       </c>
       <c r="V11" t="str">
-        <f t="shared" ref="V11:W11" si="8">U11</f>
+        <f t="shared" ref="V11:W11" si="6">U11</f>
         <v>e_w87837416-220</v>
       </c>
       <c r="W11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>e_w87837416-220</v>
       </c>
       <c r="X11" t="str">
@@ -2355,11 +2251,11 @@
         <v>11</v>
       </c>
       <c r="V12" t="str">
-        <f t="shared" ref="V12:W12" si="9">U12</f>
+        <f t="shared" ref="V12:W12" si="7">U12</f>
         <v>e_w87897292-220</v>
       </c>
       <c r="W12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>e_w87897292-220</v>
       </c>
       <c r="X12" t="str">
@@ -2435,11 +2331,11 @@
         <v>175</v>
       </c>
       <c r="V13" t="str">
-        <f t="shared" ref="V13:W13" si="10">U13</f>
+        <f t="shared" ref="V13:W13" si="8">U13</f>
         <v>e_w87928925-220</v>
       </c>
       <c r="W13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>e_w87928925-220</v>
       </c>
       <c r="X13" t="str">
@@ -2516,11 +2412,11 @@
         <v>33</v>
       </c>
       <c r="V14" t="str">
-        <f t="shared" ref="V14:W14" si="11">U14</f>
+        <f t="shared" ref="V14:W14" si="9">U14</f>
         <v>e_w89411122-220</v>
       </c>
       <c r="W14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>e_w89411122-220</v>
       </c>
       <c r="X14" t="str">
@@ -2569,11 +2465,11 @@
         <v>85</v>
       </c>
       <c r="V15" t="str">
-        <f t="shared" ref="V15:W15" si="12">U15</f>
+        <f t="shared" ref="V15:W15" si="10">U15</f>
         <v>e_w89635947-220</v>
       </c>
       <c r="W15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>e_w89635947-220</v>
       </c>
       <c r="X15" t="str">
@@ -2622,11 +2518,11 @@
         <v>83</v>
       </c>
       <c r="V16" t="str">
-        <f t="shared" ref="V16:W16" si="13">U16</f>
+        <f t="shared" ref="V16:W16" si="11">U16</f>
         <v>e_w89636266-220</v>
       </c>
       <c r="W16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>e_w89636266-220</v>
       </c>
       <c r="X16" t="str">
@@ -2675,11 +2571,11 @@
         <v>260</v>
       </c>
       <c r="V17" t="str">
-        <f t="shared" ref="V17:W17" si="14">U17</f>
+        <f t="shared" ref="V17:W17" si="12">U17</f>
         <v>e_w89636510-220</v>
       </c>
       <c r="W17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>e_w89636510-220</v>
       </c>
       <c r="X17" t="str">
@@ -2728,11 +2624,11 @@
         <v>88</v>
       </c>
       <c r="V18" t="str">
-        <f t="shared" ref="V18:W18" si="15">U18</f>
+        <f t="shared" ref="V18:W18" si="13">U18</f>
         <v>e_w89637173-220</v>
       </c>
       <c r="W18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>e_w89637173-220</v>
       </c>
       <c r="X18" t="str">
@@ -2781,11 +2677,11 @@
         <v>264</v>
       </c>
       <c r="V19" t="str">
-        <f t="shared" ref="V19:W19" si="16">U19</f>
+        <f t="shared" ref="V19:W19" si="14">U19</f>
         <v>e_w89637174-220</v>
       </c>
       <c r="W19" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>e_w89637174-220</v>
       </c>
       <c r="X19" t="str">
@@ -2834,11 +2730,11 @@
         <v>201</v>
       </c>
       <c r="V20" t="str">
-        <f t="shared" ref="V20:W20" si="17">U20</f>
+        <f t="shared" ref="V20:W20" si="15">U20</f>
         <v>e_w89637277-220</v>
       </c>
       <c r="W20" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>e_w89637277-220</v>
       </c>
       <c r="X20" t="str">
@@ -2887,11 +2783,11 @@
         <v>104</v>
       </c>
       <c r="V21" t="str">
-        <f t="shared" ref="V21:W21" si="18">U21</f>
+        <f t="shared" ref="V21:W21" si="16">U21</f>
         <v>e_w270521928-220</v>
       </c>
       <c r="W21" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>e_w270521928-220</v>
       </c>
       <c r="X21" t="str">
@@ -2940,11 +2836,11 @@
         <v>78</v>
       </c>
       <c r="V22" t="str">
-        <f t="shared" ref="V22:W22" si="19">U22</f>
+        <f t="shared" ref="V22:W22" si="17">U22</f>
         <v>e_w89664063-220</v>
       </c>
       <c r="W22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>e_w89664063-220</v>
       </c>
       <c r="X22" t="str">
@@ -2993,11 +2889,11 @@
         <v>270</v>
       </c>
       <c r="V23" t="str">
-        <f t="shared" ref="V23:W23" si="20">U23</f>
+        <f t="shared" ref="V23:W23" si="18">U23</f>
         <v>e_w89943957-220</v>
       </c>
       <c r="W23" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>e_w89943957-220</v>
       </c>
       <c r="X23" t="str">
@@ -3046,11 +2942,11 @@
         <v>272</v>
       </c>
       <c r="V24" t="str">
-        <f t="shared" ref="V24:W24" si="21">U24</f>
+        <f t="shared" ref="V24:W24" si="19">U24</f>
         <v>e_w90092620-220</v>
       </c>
       <c r="W24" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>e_w90092620-220</v>
       </c>
       <c r="X24" t="str">
@@ -3099,11 +2995,11 @@
         <v>188</v>
       </c>
       <c r="V25" t="str">
-        <f t="shared" ref="V25:W25" si="22">U25</f>
+        <f t="shared" ref="V25:W25" si="20">U25</f>
         <v>e_w90098853-220</v>
       </c>
       <c r="W25" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>e_w90098853-220</v>
       </c>
       <c r="X25" t="str">
@@ -3152,11 +3048,11 @@
         <v>227</v>
       </c>
       <c r="V26" t="str">
-        <f t="shared" ref="V26:W26" si="23">U26</f>
+        <f t="shared" ref="V26:W26" si="21">U26</f>
         <v>e_w93419960-220</v>
       </c>
       <c r="W26" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>e_w93419960-220</v>
       </c>
       <c r="X26" t="str">
@@ -3205,11 +3101,11 @@
         <v>251</v>
       </c>
       <c r="V27" t="str">
-        <f t="shared" ref="V27:W27" si="24">U27</f>
+        <f t="shared" ref="V27:W27" si="22">U27</f>
         <v>e_w93556808-220</v>
       </c>
       <c r="W27" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>e_w93556808-220</v>
       </c>
       <c r="X27" t="str">
@@ -3258,11 +3154,11 @@
         <v>168</v>
       </c>
       <c r="V28" t="str">
-        <f t="shared" ref="V28:W28" si="25">U28</f>
+        <f t="shared" ref="V28:W28" si="23">U28</f>
         <v>e_w93713118-220</v>
       </c>
       <c r="W28" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>e_w93713118-220</v>
       </c>
       <c r="X28" t="str">
@@ -3311,11 +3207,11 @@
         <v>215</v>
       </c>
       <c r="V29" t="str">
-        <f t="shared" ref="V29:W29" si="26">U29</f>
+        <f t="shared" ref="V29:W29" si="24">U29</f>
         <v>e_w93827784-220</v>
       </c>
       <c r="W29" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>e_w93827784-220</v>
       </c>
       <c r="X29" t="str">
@@ -3364,11 +3260,11 @@
         <v>281</v>
       </c>
       <c r="V30" t="str">
-        <f t="shared" ref="V30:W30" si="27">U30</f>
+        <f t="shared" ref="V30:W30" si="25">U30</f>
         <v>e_w94053861-220</v>
       </c>
       <c r="W30" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>e_w94053861-220</v>
       </c>
       <c r="X30" t="str">
@@ -3417,11 +3313,11 @@
         <v>232</v>
       </c>
       <c r="V31" t="str">
-        <f t="shared" ref="V31:W31" si="28">U31</f>
+        <f t="shared" ref="V31:W31" si="26">U31</f>
         <v>e_w94840399-220</v>
       </c>
       <c r="W31" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>e_w94840399-220</v>
       </c>
       <c r="X31" t="str">
@@ -3470,11 +3366,11 @@
         <v>285</v>
       </c>
       <c r="V32" t="str">
-        <f t="shared" ref="V32:W32" si="29">U32</f>
+        <f t="shared" ref="V32:W32" si="27">U32</f>
         <v>e_w95046918-220</v>
       </c>
       <c r="W32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>e_w95046918-220</v>
       </c>
       <c r="X32" t="str">
@@ -3523,11 +3419,11 @@
         <v>217</v>
       </c>
       <c r="V33" t="str">
-        <f t="shared" ref="V33:W33" si="30">U33</f>
+        <f t="shared" ref="V33:W33" si="28">U33</f>
         <v>e_w95048289-220</v>
       </c>
       <c r="W33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>e_w95048289-220</v>
       </c>
       <c r="X33" t="str">
@@ -3576,11 +3472,11 @@
         <v>279</v>
       </c>
       <c r="V34" t="str">
-        <f t="shared" ref="V34:W34" si="31">U34</f>
+        <f t="shared" ref="V34:W34" si="29">U34</f>
         <v>e_w95343089-220</v>
       </c>
       <c r="W34" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>e_w95343089-220</v>
       </c>
       <c r="X34" t="str">
@@ -3629,11 +3525,11 @@
         <v>125</v>
       </c>
       <c r="V35" t="str">
-        <f t="shared" ref="V35:W35" si="32">U35</f>
+        <f t="shared" ref="V35:W35" si="30">U35</f>
         <v>e_w95344674-220</v>
       </c>
       <c r="W35" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>e_w95344674-220</v>
       </c>
       <c r="X35" t="str">
@@ -3682,11 +3578,11 @@
         <v>290</v>
       </c>
       <c r="V36" t="str">
-        <f t="shared" ref="V36:W36" si="33">U36</f>
+        <f t="shared" ref="V36:W36" si="31">U36</f>
         <v>e_w95512216-220</v>
       </c>
       <c r="W36" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>e_w95512216-220</v>
       </c>
       <c r="X36" t="str">
@@ -3735,11 +3631,11 @@
         <v>127</v>
       </c>
       <c r="V37" t="str">
-        <f t="shared" ref="V37:W37" si="34">U37</f>
+        <f t="shared" ref="V37:W37" si="32">U37</f>
         <v>e_w100957314-220</v>
       </c>
       <c r="W37" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>e_w100957314-220</v>
       </c>
       <c r="X37" t="str">
@@ -3788,11 +3684,11 @@
         <v>140</v>
       </c>
       <c r="V38" t="str">
-        <f t="shared" ref="V38:W38" si="35">U38</f>
+        <f t="shared" ref="V38:W38" si="33">U38</f>
         <v>e_w119877500-220</v>
       </c>
       <c r="W38" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>e_w119877500-220</v>
       </c>
       <c r="X38" t="str">
@@ -3841,11 +3737,11 @@
         <v>146</v>
       </c>
       <c r="V39" t="str">
-        <f t="shared" ref="V39:W39" si="36">U39</f>
+        <f t="shared" ref="V39:W39" si="34">U39</f>
         <v>e_w148300699-220</v>
       </c>
       <c r="W39" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>e_w148300699-220</v>
       </c>
       <c r="X39" t="str">
@@ -3894,11 +3790,11 @@
         <v>40</v>
       </c>
       <c r="V40" t="str">
-        <f t="shared" ref="V40:W40" si="37">U40</f>
+        <f t="shared" ref="V40:W40" si="35">U40</f>
         <v>e_w156094589-220</v>
       </c>
       <c r="W40" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>e_w156094589-220</v>
       </c>
       <c r="X40" t="str">
@@ -3947,11 +3843,11 @@
         <v>148</v>
       </c>
       <c r="V41" t="str">
-        <f t="shared" ref="V41:W41" si="38">U41</f>
+        <f t="shared" ref="V41:W41" si="36">U41</f>
         <v>e_w161270797-220</v>
       </c>
       <c r="W41" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>e_w161270797-220</v>
       </c>
       <c r="X41" t="str">
@@ -4000,11 +3896,11 @@
         <v>114</v>
       </c>
       <c r="V42" t="str">
-        <f t="shared" ref="V42:W42" si="39">U42</f>
+        <f t="shared" ref="V42:W42" si="37">U42</f>
         <v>e_w167177413-220</v>
       </c>
       <c r="W42" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>e_w167177413-220</v>
       </c>
       <c r="X42" t="str">
@@ -4053,11 +3949,11 @@
         <v>24</v>
       </c>
       <c r="V43" t="str">
-        <f t="shared" ref="V43:W43" si="40">U43</f>
+        <f t="shared" ref="V43:W43" si="38">U43</f>
         <v>e_w167283894-220</v>
       </c>
       <c r="W43" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>e_w167283894-220</v>
       </c>
       <c r="X43" t="str">
@@ -4106,11 +4002,11 @@
         <v>132</v>
       </c>
       <c r="V44" t="str">
-        <f t="shared" ref="V44:W44" si="41">U44</f>
+        <f t="shared" ref="V44:W44" si="39">U44</f>
         <v>e_w167285260-220</v>
       </c>
       <c r="W44" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>e_w167285260-220</v>
       </c>
       <c r="X44" t="str">
@@ -4159,11 +4055,11 @@
         <v>51</v>
       </c>
       <c r="V45" t="str">
-        <f t="shared" ref="V45:W45" si="42">U45</f>
+        <f t="shared" ref="V45:W45" si="40">U45</f>
         <v>e_w167285336-220</v>
       </c>
       <c r="W45" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="40"/>
         <v>e_w167285336-220</v>
       </c>
       <c r="X45" t="str">
@@ -4212,11 +4108,11 @@
         <v>73</v>
       </c>
       <c r="V46" t="str">
-        <f t="shared" ref="V46:W46" si="43">U46</f>
+        <f t="shared" ref="V46:W46" si="41">U46</f>
         <v>e_w167286837-220</v>
       </c>
       <c r="W46" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="41"/>
         <v>e_w167286837-220</v>
       </c>
       <c r="X46" t="str">
@@ -4265,11 +4161,11 @@
         <v>116</v>
       </c>
       <c r="V47" t="str">
-        <f t="shared" ref="V47:W47" si="44">U47</f>
+        <f t="shared" ref="V47:W47" si="42">U47</f>
         <v>e_w167293888-220</v>
       </c>
       <c r="W47" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>e_w167293888-220</v>
       </c>
       <c r="X47" t="str">
@@ -4318,11 +4214,11 @@
         <v>165</v>
       </c>
       <c r="V48" t="str">
-        <f t="shared" ref="V48:W48" si="45">U48</f>
+        <f t="shared" ref="V48:W48" si="43">U48</f>
         <v>e_w167300914-220</v>
       </c>
       <c r="W48" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="43"/>
         <v>e_w167300914-220</v>
       </c>
       <c r="X48" t="str">
@@ -4371,11 +4267,11 @@
         <v>123</v>
       </c>
       <c r="V49" t="str">
-        <f t="shared" ref="V49:W49" si="46">U49</f>
+        <f t="shared" ref="V49:W49" si="44">U49</f>
         <v>e_w167427251-220</v>
       </c>
       <c r="W49" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="44"/>
         <v>e_w167427251-220</v>
       </c>
       <c r="X49" t="str">
@@ -4424,11 +4320,11 @@
         <v>171</v>
       </c>
       <c r="V50" t="str">
-        <f t="shared" ref="V50:W50" si="47">U50</f>
+        <f t="shared" ref="V50:W50" si="45">U50</f>
         <v>e_w167572576-220</v>
       </c>
       <c r="W50" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>e_w167572576-220</v>
       </c>
       <c r="X50" t="str">
@@ -4477,11 +4373,11 @@
         <v>58</v>
       </c>
       <c r="V51" t="str">
-        <f t="shared" ref="V51:W51" si="48">U51</f>
+        <f t="shared" ref="V51:W51" si="46">U51</f>
         <v>e_w167705537-220</v>
       </c>
       <c r="W51" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>e_w167705537-220</v>
       </c>
       <c r="X51" t="str">
@@ -4530,11 +4426,11 @@
         <v>174</v>
       </c>
       <c r="V52" t="str">
-        <f t="shared" ref="V52:W52" si="49">U52</f>
+        <f t="shared" ref="V52:W52" si="47">U52</f>
         <v>e_w169512273-220</v>
       </c>
       <c r="W52" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>e_w169512273-220</v>
       </c>
       <c r="X52" t="str">
@@ -4583,11 +4479,11 @@
         <v>76</v>
       </c>
       <c r="V53" t="str">
-        <f t="shared" ref="V53:W53" si="50">U53</f>
+        <f t="shared" ref="V53:W53" si="48">U53</f>
         <v>e_w170300247-220</v>
       </c>
       <c r="W53" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>e_w170300247-220</v>
       </c>
       <c r="X53" t="str">
@@ -4636,11 +4532,11 @@
         <v>96</v>
       </c>
       <c r="V54" t="str">
-        <f t="shared" ref="V54:W54" si="51">U54</f>
+        <f t="shared" ref="V54:W54" si="49">U54</f>
         <v>e_w180514007-220</v>
       </c>
       <c r="W54" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>e_w180514007-220</v>
       </c>
       <c r="X54" t="str">
@@ -4689,11 +4585,11 @@
         <v>98</v>
       </c>
       <c r="V55" t="str">
-        <f t="shared" ref="V55:W55" si="52">U55</f>
+        <f t="shared" ref="V55:W55" si="50">U55</f>
         <v>e_w180519027-220</v>
       </c>
       <c r="W55" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>e_w180519027-220</v>
       </c>
       <c r="X55" t="str">
@@ -4742,11 +4638,11 @@
         <v>120</v>
       </c>
       <c r="V56" t="str">
-        <f t="shared" ref="V56:W56" si="53">U56</f>
+        <f t="shared" ref="V56:W56" si="51">U56</f>
         <v>e_w187858674-220</v>
       </c>
       <c r="W56" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>e_w187858674-220</v>
       </c>
       <c r="X56" t="str">
@@ -4795,11 +4691,11 @@
         <v>184</v>
       </c>
       <c r="V57" t="str">
-        <f t="shared" ref="V57:W57" si="54">U57</f>
+        <f t="shared" ref="V57:W57" si="52">U57</f>
         <v>e_w191346761-220</v>
       </c>
       <c r="W57" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>e_w191346761-220</v>
       </c>
       <c r="X57" t="str">
@@ -4848,11 +4744,11 @@
         <v>236</v>
       </c>
       <c r="V58" t="str">
-        <f t="shared" ref="V58:W58" si="55">U58</f>
+        <f t="shared" ref="V58:W58" si="53">U58</f>
         <v>e_w232382576-220</v>
       </c>
       <c r="W58" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>e_w232382576-220</v>
       </c>
       <c r="X58" t="str">
@@ -4901,11 +4797,11 @@
         <v>91</v>
       </c>
       <c r="V59" t="str">
-        <f t="shared" ref="V59:W59" si="56">U59</f>
+        <f t="shared" ref="V59:W59" si="54">U59</f>
         <v>e_w235066414-220</v>
       </c>
       <c r="W59" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>e_w235066414-220</v>
       </c>
       <c r="X59" t="str">
@@ -4954,11 +4850,11 @@
         <v>203</v>
       </c>
       <c r="V60" t="str">
-        <f t="shared" ref="V60:W60" si="57">U60</f>
+        <f t="shared" ref="V60:W60" si="55">U60</f>
         <v>e_w255873374-220</v>
       </c>
       <c r="W60" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>e_w255873374-220</v>
       </c>
       <c r="X60" t="str">
@@ -5007,11 +4903,11 @@
         <v>63</v>
       </c>
       <c r="V61" t="str">
-        <f t="shared" ref="V61:W61" si="58">U61</f>
+        <f t="shared" ref="V61:W61" si="56">U61</f>
         <v>e_w268826084-220</v>
       </c>
       <c r="W61" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>e_w268826084-220</v>
       </c>
       <c r="X61" t="str">
@@ -5060,11 +4956,11 @@
         <v>101</v>
       </c>
       <c r="V62" t="str">
-        <f t="shared" ref="V62:W62" si="59">U62</f>
+        <f t="shared" ref="V62:W62" si="57">U62</f>
         <v>e_w268841395-220</v>
       </c>
       <c r="W62" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>e_w268841395-220</v>
       </c>
       <c r="X62" t="str">
@@ -5113,11 +5009,11 @@
         <v>67</v>
       </c>
       <c r="V63" t="str">
-        <f t="shared" ref="V63:W63" si="60">U63</f>
+        <f t="shared" ref="V63:W63" si="58">U63</f>
         <v>e_w270012796-220</v>
       </c>
       <c r="W63" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>e_w270012796-220</v>
       </c>
       <c r="X63" t="str">
@@ -5166,11 +5062,11 @@
         <v>157</v>
       </c>
       <c r="V64" t="str">
-        <f t="shared" ref="V64:W64" si="61">U64</f>
+        <f t="shared" ref="V64:W64" si="59">U64</f>
         <v>e_w270018358-220</v>
       </c>
       <c r="W64" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>e_w270018358-220</v>
       </c>
       <c r="X64" t="str">
@@ -5219,11 +5115,11 @@
         <v>141</v>
       </c>
       <c r="V65" t="str">
-        <f t="shared" ref="V65:W65" si="62">U65</f>
+        <f t="shared" ref="V65:W65" si="60">U65</f>
         <v>e_w270022030-220</v>
       </c>
       <c r="W65" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>e_w270022030-220</v>
       </c>
       <c r="X65" t="str">
@@ -5272,11 +5168,11 @@
         <v>159</v>
       </c>
       <c r="V66" t="str">
-        <f t="shared" ref="V66:W66" si="63">U66</f>
+        <f t="shared" ref="V66:W66" si="61">U66</f>
         <v>e_w270554679-220</v>
       </c>
       <c r="W66" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>e_w270554679-220</v>
       </c>
       <c r="X66" t="str">
@@ -5325,11 +5221,11 @@
         <v>205</v>
       </c>
       <c r="V67" t="str">
-        <f t="shared" ref="V67:W67" si="64">U67</f>
+        <f t="shared" ref="V67:W67" si="62">U67</f>
         <v>e_w270556206-220</v>
       </c>
       <c r="W67" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="62"/>
         <v>e_w270556206-220</v>
       </c>
       <c r="X67" t="str">
@@ -5378,11 +5274,11 @@
         <v>107</v>
       </c>
       <c r="V68" t="str">
-        <f t="shared" ref="V68:W68" si="65">U68</f>
+        <f t="shared" ref="V68:W68" si="63">U68</f>
         <v>e_w272195826-220</v>
       </c>
       <c r="W68" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>e_w272195826-220</v>
       </c>
       <c r="X68" t="str">
@@ -5431,11 +5327,11 @@
         <v>208</v>
       </c>
       <c r="V69" t="str">
-        <f t="shared" ref="V69:W69" si="66">U69</f>
+        <f t="shared" ref="V69:W69" si="64">U69</f>
         <v>e_w272522517-220</v>
       </c>
       <c r="W69" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>e_w272522517-220</v>
       </c>
       <c r="X69" t="str">
@@ -5484,15 +5380,15 @@
         <v>27</v>
       </c>
       <c r="V70" t="str">
-        <f t="shared" ref="V70:W70" si="67">U70</f>
+        <f t="shared" ref="V70:W70" si="65">U70</f>
         <v>e_w275188676-220</v>
       </c>
       <c r="W70" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>e_w275188676-220</v>
       </c>
       <c r="X70" t="str">
-        <f t="shared" ref="X70:X128" si="68">"TU_"&amp;U70</f>
+        <f t="shared" ref="X70:X128" si="66">"TU_"&amp;U70</f>
         <v>TU_e_w275188676-220</v>
       </c>
       <c r="Y70" t="s">
@@ -5537,15 +5433,15 @@
         <v>219</v>
       </c>
       <c r="V71" t="str">
-        <f t="shared" ref="V71:W71" si="69">U71</f>
+        <f t="shared" ref="V71:W71" si="67">U71</f>
         <v>e_w341099346-220</v>
       </c>
       <c r="W71" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>e_w341099346-220</v>
       </c>
       <c r="X71" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w341099346-220</v>
       </c>
       <c r="Y71" t="s">
@@ -5590,15 +5486,15 @@
         <v>223</v>
       </c>
       <c r="V72" t="str">
-        <f t="shared" ref="V72:W72" si="70">U72</f>
+        <f t="shared" ref="V72:W72" si="68">U72</f>
         <v>e_w359449581-220</v>
       </c>
       <c r="W72" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>e_w359449581-220</v>
       </c>
       <c r="X72" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w359449581-220</v>
       </c>
       <c r="Y72" t="s">
@@ -5643,15 +5539,15 @@
         <v>226</v>
       </c>
       <c r="V73" t="str">
-        <f t="shared" ref="V73:W73" si="71">U73</f>
+        <f t="shared" ref="V73:W73" si="69">U73</f>
         <v>e_w409049317-220</v>
       </c>
       <c r="W73" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>e_w409049317-220</v>
       </c>
       <c r="X73" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w409049317-220</v>
       </c>
       <c r="Y73" t="s">
@@ -5696,15 +5592,15 @@
         <v>230</v>
       </c>
       <c r="V74" t="str">
-        <f t="shared" ref="V74:W74" si="72">U74</f>
+        <f t="shared" ref="V74:W74" si="70">U74</f>
         <v>e_w412589726-220</v>
       </c>
       <c r="W74" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>e_w412589726-220</v>
       </c>
       <c r="X74" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w412589726-220</v>
       </c>
       <c r="Y74" t="s">
@@ -5749,15 +5645,15 @@
         <v>181</v>
       </c>
       <c r="V75" t="str">
-        <f t="shared" ref="V75:W75" si="73">U75</f>
+        <f t="shared" ref="V75:W75" si="71">U75</f>
         <v>e_w414953388-220</v>
       </c>
       <c r="W75" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>e_w414953388-220</v>
       </c>
       <c r="X75" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w414953388-220</v>
       </c>
       <c r="Y75" t="s">
@@ -5802,15 +5698,15 @@
         <v>238</v>
       </c>
       <c r="V76" t="str">
-        <f t="shared" ref="V76:W76" si="74">U76</f>
+        <f t="shared" ref="V76:W76" si="72">U76</f>
         <v>e_w627162826-220</v>
       </c>
       <c r="W76" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>e_w627162826-220</v>
       </c>
       <c r="X76" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w627162826-220</v>
       </c>
       <c r="Y76" t="s">
@@ -5855,15 +5751,15 @@
         <v>242</v>
       </c>
       <c r="V77" t="str">
-        <f t="shared" ref="V77:W77" si="75">U77</f>
+        <f t="shared" ref="V77:W77" si="73">U77</f>
         <v>e_w849110529-220</v>
       </c>
       <c r="W77" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>e_w849110529-220</v>
       </c>
       <c r="X77" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w849110529-220</v>
       </c>
       <c r="Y77" t="s">
@@ -5908,15 +5804,15 @@
         <v>144</v>
       </c>
       <c r="V78" t="str">
-        <f t="shared" ref="V78:W78" si="76">U78</f>
+        <f t="shared" ref="V78:W78" si="74">U78</f>
         <v>e_w907631032-220</v>
       </c>
       <c r="W78" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>e_w907631032-220</v>
       </c>
       <c r="X78" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w907631032-220</v>
       </c>
       <c r="Y78" t="s">
@@ -5961,15 +5857,15 @@
         <v>129</v>
       </c>
       <c r="V79" t="str">
-        <f t="shared" ref="V79:W79" si="77">U79</f>
+        <f t="shared" ref="V79:W79" si="75">U79</f>
         <v>e_w1018655038-220</v>
       </c>
       <c r="W79" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="75"/>
         <v>e_w1018655038-220</v>
       </c>
       <c r="X79" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w1018655038-220</v>
       </c>
       <c r="Y79" t="s">
@@ -6014,15 +5910,15 @@
         <v>138</v>
       </c>
       <c r="V80" t="str">
-        <f t="shared" ref="V80:W80" si="78">U80</f>
+        <f t="shared" ref="V80:W80" si="76">U80</f>
         <v>e_w1026587442-220</v>
       </c>
       <c r="W80" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>e_w1026587442-220</v>
       </c>
       <c r="X80" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w1026587442-220</v>
       </c>
       <c r="Y80" t="s">
@@ -6067,15 +5963,15 @@
         <v>30</v>
       </c>
       <c r="V81" t="str">
-        <f t="shared" ref="V81:W81" si="79">U81</f>
+        <f t="shared" ref="V81:W81" si="77">U81</f>
         <v>e_w1034927052-220</v>
       </c>
       <c r="W81" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>e_w1034927052-220</v>
       </c>
       <c r="X81" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w1034927052-220</v>
       </c>
       <c r="Y81" t="s">
@@ -6120,15 +6016,15 @@
         <v>134</v>
       </c>
       <c r="V82" t="str">
-        <f t="shared" ref="V82:W82" si="80">U82</f>
+        <f t="shared" ref="V82:W82" si="78">U82</f>
         <v>e_w1099619174-220</v>
       </c>
       <c r="W82" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>e_w1099619174-220</v>
       </c>
       <c r="X82" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w1099619174-220</v>
       </c>
       <c r="Y82" t="s">
@@ -6173,15 +6069,15 @@
         <v>137</v>
       </c>
       <c r="V83" t="str">
-        <f t="shared" ref="V83:W83" si="81">U83</f>
+        <f t="shared" ref="V83:W83" si="79">U83</f>
         <v>e_w1167708390-220</v>
       </c>
       <c r="W83" t="str">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>e_w1167708390-220</v>
       </c>
       <c r="X83" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w1167708390-220</v>
       </c>
       <c r="Y83" t="s">
@@ -6226,15 +6122,15 @@
         <v>143</v>
       </c>
       <c r="V84" t="str">
-        <f t="shared" ref="V84:W84" si="82">U84</f>
+        <f t="shared" ref="V84:W84" si="80">U84</f>
         <v>e_w1363994055-220</v>
       </c>
       <c r="W84" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>e_w1363994055-220</v>
       </c>
       <c r="X84" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_w1363994055-220</v>
       </c>
       <c r="Y84" t="s">
@@ -6279,15 +6175,15 @@
         <v>122</v>
       </c>
       <c r="V85" t="str">
-        <f t="shared" ref="V85:W85" si="83">U85</f>
+        <f t="shared" ref="V85:W85" si="81">U85</f>
         <v>e_r17609399-220</v>
       </c>
       <c r="W85" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>e_r17609399-220</v>
       </c>
       <c r="X85" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_r17609399-220</v>
       </c>
       <c r="Y85" t="s">
@@ -6332,15 +6228,15 @@
         <v>55</v>
       </c>
       <c r="V86" t="str">
-        <f t="shared" ref="V86:W86" si="84">U86</f>
+        <f t="shared" ref="V86:W86" si="82">U86</f>
         <v>e_NZ26-220</v>
       </c>
       <c r="W86" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>e_NZ26-220</v>
       </c>
       <c r="X86" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ26-220</v>
       </c>
       <c r="Y86" t="s">
@@ -6385,15 +6281,15 @@
         <v>60</v>
       </c>
       <c r="V87" t="str">
-        <f t="shared" ref="V87:W87" si="85">U87</f>
+        <f t="shared" ref="V87:W87" si="83">U87</f>
         <v>e_NZ28-220</v>
       </c>
       <c r="W87" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>e_NZ28-220</v>
       </c>
       <c r="X87" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ28-220</v>
       </c>
       <c r="Y87" t="s">
@@ -6438,15 +6334,15 @@
         <v>90</v>
       </c>
       <c r="V88" t="str">
-        <f t="shared" ref="V88:W88" si="86">U88</f>
+        <f t="shared" ref="V88:W88" si="84">U88</f>
         <v>e_NZ4-220</v>
       </c>
       <c r="W88" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>e_NZ4-220</v>
       </c>
       <c r="X88" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ4-220</v>
       </c>
       <c r="Y88" t="s">
@@ -6491,15 +6387,15 @@
         <v>42</v>
       </c>
       <c r="V89" t="str">
-        <f t="shared" ref="V89:W89" si="87">U89</f>
+        <f t="shared" ref="V89:W89" si="85">U89</f>
         <v>e_NZ20-220</v>
       </c>
       <c r="W89" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>e_NZ20-220</v>
       </c>
       <c r="X89" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ20-220</v>
       </c>
       <c r="Y89" t="s">
@@ -6544,15 +6440,15 @@
         <v>35</v>
       </c>
       <c r="V90" t="str">
-        <f t="shared" ref="V90:W90" si="88">U90</f>
+        <f t="shared" ref="V90:W90" si="86">U90</f>
         <v>e_NZ19-220</v>
       </c>
       <c r="W90" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>e_NZ19-220</v>
       </c>
       <c r="X90" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ19-220</v>
       </c>
       <c r="Y90" t="s">
@@ -6597,15 +6493,15 @@
         <v>81</v>
       </c>
       <c r="V91" t="str">
-        <f t="shared" ref="V91:W91" si="89">U91</f>
+        <f t="shared" ref="V91:W91" si="87">U91</f>
         <v>e_NZ37-220</v>
       </c>
       <c r="W91" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>e_NZ37-220</v>
       </c>
       <c r="X91" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ37-220</v>
       </c>
       <c r="Y91" t="s">
@@ -6650,15 +6546,15 @@
         <v>80</v>
       </c>
       <c r="V92" t="str">
-        <f t="shared" ref="V92:W92" si="90">U92</f>
+        <f t="shared" ref="V92:W92" si="88">U92</f>
         <v>e_NZ36-220</v>
       </c>
       <c r="W92" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>e_NZ36-220</v>
       </c>
       <c r="X92" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ36-220</v>
       </c>
       <c r="Y92" t="s">
@@ -6703,15 +6599,15 @@
         <v>70</v>
       </c>
       <c r="V93" t="str">
-        <f t="shared" ref="V93:W93" si="91">U93</f>
+        <f t="shared" ref="V93:W93" si="89">U93</f>
         <v>e_NZ34-220</v>
       </c>
       <c r="W93" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>e_NZ34-220</v>
       </c>
       <c r="X93" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ34-220</v>
       </c>
       <c r="Y93" t="s">
@@ -6756,15 +6652,15 @@
         <v>87</v>
       </c>
       <c r="V94" t="str">
-        <f t="shared" ref="V94:W94" si="92">U94</f>
+        <f t="shared" ref="V94:W94" si="90">U94</f>
         <v>e_NZ39-220</v>
       </c>
       <c r="W94" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>e_NZ39-220</v>
       </c>
       <c r="X94" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ39-220</v>
       </c>
       <c r="Y94" t="s">
@@ -6809,15 +6705,15 @@
         <v>61</v>
       </c>
       <c r="V95" t="str">
-        <f t="shared" ref="V95:W95" si="93">U95</f>
+        <f t="shared" ref="V95:W95" si="91">U95</f>
         <v>e_NZ29-220</v>
       </c>
       <c r="W95" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>e_NZ29-220</v>
       </c>
       <c r="X95" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ29-220</v>
       </c>
       <c r="Y95" t="s">
@@ -6862,15 +6758,15 @@
         <v>103</v>
       </c>
       <c r="V96" t="str">
-        <f t="shared" ref="V96:W96" si="94">U96</f>
+        <f t="shared" ref="V96:W96" si="92">U96</f>
         <v>e_NZ42-220</v>
       </c>
       <c r="W96" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>e_NZ42-220</v>
       </c>
       <c r="X96" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ42-220</v>
       </c>
       <c r="Y96" t="s">
@@ -6915,15 +6811,15 @@
         <v>100</v>
       </c>
       <c r="V97" t="str">
-        <f t="shared" ref="V97:W97" si="95">U97</f>
+        <f t="shared" ref="V97:W97" si="93">U97</f>
         <v>e_NZ41-220</v>
       </c>
       <c r="W97" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>e_NZ41-220</v>
       </c>
       <c r="X97" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ41-220</v>
       </c>
       <c r="Y97" t="s">
@@ -6968,15 +6864,15 @@
         <v>106</v>
       </c>
       <c r="V98" t="str">
-        <f t="shared" ref="V98:W98" si="96">U98</f>
+        <f t="shared" ref="V98:W98" si="94">U98</f>
         <v>e_NZ43-220</v>
       </c>
       <c r="W98" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>e_NZ43-220</v>
       </c>
       <c r="X98" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ43-220</v>
       </c>
       <c r="Y98" t="s">
@@ -7021,15 +6917,15 @@
         <v>14</v>
       </c>
       <c r="V99" t="str">
-        <f t="shared" ref="V99:W99" si="97">U99</f>
+        <f t="shared" ref="V99:W99" si="95">U99</f>
         <v>e_NZ10-220</v>
       </c>
       <c r="W99" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>e_NZ10-220</v>
       </c>
       <c r="X99" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ10-220</v>
       </c>
       <c r="Y99" t="s">
@@ -7074,15 +6970,15 @@
         <v>47</v>
       </c>
       <c r="V100" t="str">
-        <f t="shared" ref="V100:W100" si="98">U100</f>
+        <f t="shared" ref="V100:W100" si="96">U100</f>
         <v>e_NZ21-220</v>
       </c>
       <c r="W100" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>e_NZ21-220</v>
       </c>
       <c r="X100" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ21-220</v>
       </c>
       <c r="Y100" t="s">
@@ -7127,15 +7023,15 @@
         <v>26</v>
       </c>
       <c r="V101" t="str">
-        <f t="shared" ref="V101:W101" si="99">U101</f>
+        <f t="shared" ref="V101:W101" si="97">U101</f>
         <v>e_NZ16-220</v>
       </c>
       <c r="W101" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>e_NZ16-220</v>
       </c>
       <c r="X101" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ16-220</v>
       </c>
       <c r="Y101" t="s">
@@ -7180,15 +7076,15 @@
         <v>72</v>
       </c>
       <c r="V102" t="str">
-        <f t="shared" ref="V102:W102" si="100">U102</f>
+        <f t="shared" ref="V102:W102" si="98">U102</f>
         <v>e_NZ32-220</v>
       </c>
       <c r="W102" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>e_NZ32-220</v>
       </c>
       <c r="X102" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ32-220</v>
       </c>
       <c r="Y102" t="s">
@@ -7233,15 +7129,15 @@
         <v>113</v>
       </c>
       <c r="V103" t="str">
-        <f t="shared" ref="V103:W103" si="101">U103</f>
+        <f t="shared" ref="V103:W103" si="99">U103</f>
         <v>e_NZ7-220</v>
       </c>
       <c r="W103" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>e_NZ7-220</v>
       </c>
       <c r="X103" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ7-220</v>
       </c>
       <c r="Y103" t="s">
@@ -7286,15 +7182,15 @@
         <v>53</v>
       </c>
       <c r="V104" t="str">
-        <f t="shared" ref="V104:W104" si="102">U104</f>
+        <f t="shared" ref="V104:W104" si="100">U104</f>
         <v>e_NZ25-220</v>
       </c>
       <c r="W104" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>e_NZ25-220</v>
       </c>
       <c r="X104" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ25-220</v>
       </c>
       <c r="Y104" t="s">
@@ -7339,15 +7235,15 @@
         <v>50</v>
       </c>
       <c r="V105" t="str">
-        <f t="shared" ref="V105:W105" si="103">U105</f>
+        <f t="shared" ref="V105:W105" si="101">U105</f>
         <v>e_NZ24-220</v>
       </c>
       <c r="W105" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>e_NZ24-220</v>
       </c>
       <c r="X105" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ24-220</v>
       </c>
       <c r="Y105" t="s">
@@ -7392,15 +7288,15 @@
         <v>95</v>
       </c>
       <c r="V106" t="str">
-        <f t="shared" ref="V106:W106" si="104">U106</f>
+        <f t="shared" ref="V106:W106" si="102">U106</f>
         <v>e_NZ40-220</v>
       </c>
       <c r="W106" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>e_NZ40-220</v>
       </c>
       <c r="X106" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ40-220</v>
       </c>
       <c r="Y106" t="s">
@@ -7445,15 +7341,15 @@
         <v>118</v>
       </c>
       <c r="V107" t="str">
-        <f t="shared" ref="V107:W107" si="105">U107</f>
+        <f t="shared" ref="V107:W107" si="103">U107</f>
         <v>e_NZ9-220</v>
       </c>
       <c r="W107" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>e_NZ9-220</v>
       </c>
       <c r="X107" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ9-220</v>
       </c>
       <c r="Y107" t="s">
@@ -7498,15 +7394,15 @@
         <v>17</v>
       </c>
       <c r="V108" t="str">
-        <f t="shared" ref="V108:W108" si="106">U108</f>
+        <f t="shared" ref="V108:W108" si="104">U108</f>
         <v>e_NZ11-220</v>
       </c>
       <c r="W108" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>e_NZ11-220</v>
       </c>
       <c r="X108" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ11-220</v>
       </c>
       <c r="Y108" t="s">
@@ -7551,15 +7447,15 @@
         <v>18</v>
       </c>
       <c r="V109" t="str">
-        <f t="shared" ref="V109:W109" si="107">U109</f>
+        <f t="shared" ref="V109:W109" si="105">U109</f>
         <v>e_NZ12-220</v>
       </c>
       <c r="W109" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>e_NZ12-220</v>
       </c>
       <c r="X109" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ12-220</v>
       </c>
       <c r="Y109" t="s">
@@ -7604,15 +7500,15 @@
         <v>57</v>
       </c>
       <c r="V110" t="str">
-        <f t="shared" ref="V110:W110" si="108">U110</f>
+        <f t="shared" ref="V110:W110" si="106">U110</f>
         <v>e_NZ27-220</v>
       </c>
       <c r="W110" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>e_NZ27-220</v>
       </c>
       <c r="X110" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ27-220</v>
       </c>
       <c r="Y110" t="s">
@@ -7657,15 +7553,15 @@
         <v>109</v>
       </c>
       <c r="V111" t="str">
-        <f t="shared" ref="V111:W111" si="109">U111</f>
+        <f t="shared" ref="V111:W111" si="107">U111</f>
         <v>e_NZ5-220</v>
       </c>
       <c r="W111" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>e_NZ5-220</v>
       </c>
       <c r="X111" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ5-220</v>
       </c>
       <c r="Y111" t="s">
@@ -7710,15 +7606,15 @@
         <v>37</v>
       </c>
       <c r="V112" t="str">
-        <f t="shared" ref="V112:W112" si="110">U112</f>
+        <f t="shared" ref="V112:W112" si="108">U112</f>
         <v>e_NZ2-220</v>
       </c>
       <c r="W112" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>e_NZ2-220</v>
       </c>
       <c r="X112" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ2-220</v>
       </c>
       <c r="Y112" t="s">
@@ -7763,15 +7659,15 @@
         <v>38</v>
       </c>
       <c r="V113" t="str">
-        <f t="shared" ref="V113:W113" si="111">U113</f>
+        <f t="shared" ref="V113:W113" si="109">U113</f>
         <v>e_NZ3-220</v>
       </c>
       <c r="W113" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>e_NZ3-220</v>
       </c>
       <c r="X113" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ3-220</v>
       </c>
       <c r="Y113" t="s">
@@ -7816,15 +7712,15 @@
         <v>32</v>
       </c>
       <c r="V114" t="str">
-        <f t="shared" ref="V114:W114" si="112">U114</f>
+        <f t="shared" ref="V114:W114" si="110">U114</f>
         <v>e_NZ18-220</v>
       </c>
       <c r="W114" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>e_NZ18-220</v>
       </c>
       <c r="X114" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ18-220</v>
       </c>
       <c r="Y114" t="s">
@@ -7869,15 +7765,15 @@
         <v>20</v>
       </c>
       <c r="V115" t="str">
-        <f t="shared" ref="V115:W115" si="113">U115</f>
+        <f t="shared" ref="V115:W115" si="111">U115</f>
         <v>e_NZ6-220</v>
       </c>
       <c r="W115" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>e_NZ6-220</v>
       </c>
       <c r="X115" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ6-220</v>
       </c>
       <c r="Y115" t="s">
@@ -7922,15 +7818,15 @@
         <v>66</v>
       </c>
       <c r="V116" t="str">
-        <f t="shared" ref="V116:W116" si="114">U116</f>
+        <f t="shared" ref="V116:W116" si="112">U116</f>
         <v>e_NZ30-220</v>
       </c>
       <c r="W116" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="112"/>
         <v>e_NZ30-220</v>
       </c>
       <c r="X116" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ30-220</v>
       </c>
       <c r="Y116" t="s">
@@ -7975,15 +7871,15 @@
         <v>10</v>
       </c>
       <c r="V117" t="str">
-        <f t="shared" ref="V117:W117" si="115">U117</f>
+        <f t="shared" ref="V117:W117" si="113">U117</f>
         <v>e_NZ1-220</v>
       </c>
       <c r="W117" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>e_NZ1-220</v>
       </c>
       <c r="X117" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ1-220</v>
       </c>
       <c r="Y117" t="s">
@@ -8028,15 +7924,15 @@
         <v>29</v>
       </c>
       <c r="V118" t="str">
-        <f t="shared" ref="V118:W118" si="116">U118</f>
+        <f t="shared" ref="V118:W118" si="114">U118</f>
         <v>e_NZ17-220</v>
       </c>
       <c r="W118" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>e_NZ17-220</v>
       </c>
       <c r="X118" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ17-220</v>
       </c>
       <c r="Y118" t="s">
@@ -8081,15 +7977,15 @@
         <v>43</v>
       </c>
       <c r="V119" t="str">
-        <f t="shared" ref="V119:W119" si="117">U119</f>
+        <f t="shared" ref="V119:W119" si="115">U119</f>
         <v>e_NZ22-220</v>
       </c>
       <c r="W119" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>e_NZ22-220</v>
       </c>
       <c r="X119" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ22-220</v>
       </c>
       <c r="Y119" t="s">
@@ -8134,15 +8030,15 @@
         <v>69</v>
       </c>
       <c r="V120" t="str">
-        <f t="shared" ref="V120:W120" si="118">U120</f>
+        <f t="shared" ref="V120:W120" si="116">U120</f>
         <v>e_NZ31-220</v>
       </c>
       <c r="W120" t="str">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>e_NZ31-220</v>
       </c>
       <c r="X120" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ31-220</v>
       </c>
       <c r="Y120" t="s">
@@ -8187,15 +8083,15 @@
         <v>23</v>
       </c>
       <c r="V121" t="str">
-        <f t="shared" ref="V121:W121" si="119">U121</f>
+        <f t="shared" ref="V121:W121" si="117">U121</f>
         <v>e_NZ13-220</v>
       </c>
       <c r="W121" t="str">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>e_NZ13-220</v>
       </c>
       <c r="X121" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ13-220</v>
       </c>
       <c r="Y121" t="s">
@@ -8240,15 +8136,15 @@
         <v>247</v>
       </c>
       <c r="V122" t="str">
-        <f t="shared" ref="V122:W122" si="120">U122</f>
+        <f t="shared" ref="V122:W122" si="118">U122</f>
         <v>e_NZ14-220</v>
       </c>
       <c r="W122" t="str">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>e_NZ14-220</v>
       </c>
       <c r="X122" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ14-220</v>
       </c>
       <c r="Y122" t="s">
@@ -8293,15 +8189,15 @@
         <v>45</v>
       </c>
       <c r="V123" t="str">
-        <f t="shared" ref="V123:W123" si="121">U123</f>
+        <f t="shared" ref="V123:W123" si="119">U123</f>
         <v>e_NZ23-220</v>
       </c>
       <c r="W123" t="str">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>e_NZ23-220</v>
       </c>
       <c r="X123" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ23-220</v>
       </c>
       <c r="Y123" t="s">
@@ -8346,15 +8242,15 @@
         <v>265</v>
       </c>
       <c r="V124" t="str">
-        <f t="shared" ref="V124:W124" si="122">U124</f>
+        <f t="shared" ref="V124:W124" si="120">U124</f>
         <v>e_NZ38-220</v>
       </c>
       <c r="W124" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>e_NZ38-220</v>
       </c>
       <c r="X124" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ38-220</v>
       </c>
       <c r="Y124" t="s">
@@ -8399,15 +8295,15 @@
         <v>15</v>
       </c>
       <c r="V125" t="str">
-        <f t="shared" ref="V125:W125" si="123">U125</f>
+        <f t="shared" ref="V125:W125" si="121">U125</f>
         <v>e_NZ8-220</v>
       </c>
       <c r="W125" t="str">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>e_NZ8-220</v>
       </c>
       <c r="X125" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ8-220</v>
       </c>
       <c r="Y125" t="s">
@@ -8452,15 +8348,15 @@
         <v>256</v>
       </c>
       <c r="V126" t="str">
-        <f t="shared" ref="V126:W126" si="124">U126</f>
+        <f t="shared" ref="V126:W126" si="122">U126</f>
         <v>e_NZ35-220</v>
       </c>
       <c r="W126" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>e_NZ35-220</v>
       </c>
       <c r="X126" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ35-220</v>
       </c>
       <c r="Y126" t="s">
@@ -8505,15 +8401,15 @@
         <v>261</v>
       </c>
       <c r="V127" t="str">
-        <f t="shared" ref="V127:W127" si="125">U127</f>
+        <f t="shared" ref="V127:W127" si="123">U127</f>
         <v>e_NZ33-220</v>
       </c>
       <c r="W127" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>e_NZ33-220</v>
       </c>
       <c r="X127" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ33-220</v>
       </c>
       <c r="Y127" t="s">
@@ -8558,15 +8454,15 @@
         <v>154</v>
       </c>
       <c r="V128" t="str">
-        <f t="shared" ref="V128:W128" si="126">U128</f>
+        <f t="shared" ref="V128:W128" si="124">U128</f>
         <v>e_NZ15-220</v>
       </c>
       <c r="W128" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>e_NZ15-220</v>
       </c>
       <c r="X128" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>TU_e_NZ15-220</v>
       </c>
       <c r="Y128" t="s">
@@ -9509,23 +9405,44 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83540081-FFBC-45CD-9805-E20E8DB7BB2A}">
-  <dimension ref="C7:E62"/>
+  <dimension ref="C7:O62"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16384" width="9.19921875" style="2"/>
+    <col min="1" max="2" width="9.19921875" style="2"/>
+    <col min="3" max="3" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="9.19921875" style="2"/>
+    <col min="9" max="9" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.73046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.19921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C8" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+    </row>
+    <row r="9" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C9" s="4" t="s">
         <v>399</v>
       </c>
@@ -9535,8 +9452,29 @@
       <c r="E9" s="5" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C10" s="5" t="s">
         <v>393</v>
       </c>
@@ -9544,20 +9482,114 @@
       <c r="E10" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I10" t="s">
+        <v>393</v>
+      </c>
+      <c r="J10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>396</v>
+      </c>
+      <c r="L10" t="s">
+        <v>397</v>
+      </c>
+      <c r="M10" t="str">
+        <f>K10</f>
+        <v>gas</v>
+      </c>
+      <c r="N10" t="str">
+        <f>"TU_"&amp;L10</f>
+        <v>TU_ELCNGA</v>
+      </c>
+      <c r="O10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C11" s="5" t="s">
         <v>394</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="6"/>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I11" t="s">
+        <v>393</v>
+      </c>
+      <c r="J11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" t="s">
+        <v>412</v>
+      </c>
+      <c r="L11" t="s">
+        <v>405</v>
+      </c>
+      <c r="M11" t="str">
+        <f>K11</f>
+        <v>coal</v>
+      </c>
+      <c r="N11" t="str">
+        <f>"TU_ELC"&amp;L11</f>
+        <v>TU_ELCCOA</v>
+      </c>
+      <c r="O11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="I12" t="s">
+        <v>393</v>
+      </c>
+      <c r="J12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" t="s">
+        <v>413</v>
+      </c>
+      <c r="L12" t="s">
+        <v>401</v>
+      </c>
+      <c r="M12" t="str">
+        <f>K12</f>
+        <v>oil</v>
+      </c>
+      <c r="N12" t="str">
+        <f>"TU_ELC"&amp;L12</f>
+        <v>TU_ELCDSL</v>
+      </c>
+      <c r="O12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C13" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I13" t="s">
+        <v>393</v>
+      </c>
+      <c r="J13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" t="s">
+        <v>414</v>
+      </c>
+      <c r="L13" t="s">
+        <v>415</v>
+      </c>
+      <c r="M13" t="str">
+        <f>K13</f>
+        <v>bioenergy</v>
+      </c>
+      <c r="N13" t="str">
+        <f>"TU_ELC"&amp;L13</f>
+        <v>TU_ELCWOD</v>
+      </c>
+      <c r="O13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C14" s="4" t="s">
         <v>400</v>
       </c>
@@ -9567,8 +9599,31 @@
       <c r="E14" s="5" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I14" t="s">
+        <v>393</v>
+      </c>
+      <c r="J14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" t="s">
+        <v>416</v>
+      </c>
+      <c r="L14" t="s">
+        <v>417</v>
+      </c>
+      <c r="M14" t="str">
+        <f>K14</f>
+        <v>geothermal</v>
+      </c>
+      <c r="N14" t="str">
+        <f>"TU_ELC"&amp;L14</f>
+        <v>TU_ELCGEO</v>
+      </c>
+      <c r="O14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15" ht="14.25" x14ac:dyDescent="0.45">
       <c r="C15" s="5" t="s">
         <v>393</v>
       </c>
@@ -9576,8 +9631,31 @@
       <c r="E15" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="I15" t="s">
+        <v>393</v>
+      </c>
+      <c r="J15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" t="s">
+        <v>418</v>
+      </c>
+      <c r="L15" t="s">
+        <v>419</v>
+      </c>
+      <c r="M15" t="str">
+        <f>K15</f>
+        <v>hydro</v>
+      </c>
+      <c r="N15" t="str">
+        <f>"TU_ELC"&amp;L15</f>
+        <v>TU_ELCHYD</v>
+      </c>
+      <c r="O15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
       <c r="C16" s="5" t="s">
         <v>394</v>
       </c>
